--- a/research/traditional_assets/database/data/new_zealand/new_zealand_retail_general.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,13 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.09157192634724312</v>
+      </c>
+      <c r="C2">
+        <v>566.217466623008</v>
+      </c>
+      <c r="D2">
+        <v>554.059466623008</v>
       </c>
       <c r="E2">
-        <v>-483</v>
+        <v>-476.158</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.842000000000001</v>
       </c>
       <c r="G2">
         <v>19</v>
@@ -1442,43 +1451,45 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.6133436</v>
       </c>
       <c r="N2">
-        <v>-4.733333333333334</v>
+        <v>-6.346676933333335</v>
       </c>
       <c r="O2">
-        <v>-1.325333333333334</v>
+        <v>-1.777069541333334</v>
       </c>
       <c r="P2">
-        <v>-3.408</v>
+        <v>-4.569607392000001</v>
       </c>
       <c r="Q2">
-        <v>89.992</v>
+        <v>88.83039260800001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.08815845545996417</v>
+      </c>
+      <c r="T2">
+        <v>0.9782553224010202</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-0.8214823756906673</v>
+      </c>
+      <c r="W2">
+        <v>0.4295055441878594</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-2.933865627466669</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1486,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09157192634724312</v>
+        <v>0.09347192634724312</v>
       </c>
       <c r="C3">
-        <v>566.217466623008</v>
+        <v>548.1519649552893</v>
       </c>
       <c r="D3">
-        <v>554.059466623008</v>
+        <v>542.8359649552892</v>
       </c>
       <c r="E3">
-        <v>-476.158</v>
+        <v>-469.316</v>
       </c>
       <c r="F3">
-        <v>6.842000000000001</v>
+        <v>13.684</v>
       </c>
       <c r="G3">
         <v>19</v>
@@ -1522,37 +1533,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M3">
-        <v>1.6133436</v>
+        <v>3.2266872</v>
       </c>
       <c r="N3">
-        <v>-6.346676933333335</v>
+        <v>-7.960020533333335</v>
       </c>
       <c r="O3">
-        <v>-1.777069541333334</v>
+        <v>-2.228805749333334</v>
       </c>
       <c r="P3">
-        <v>-4.569607392000001</v>
+        <v>-5.731214784000001</v>
       </c>
       <c r="Q3">
-        <v>88.83039260800001</v>
+        <v>87.668785216</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08815845545996417</v>
+        <v>0.08859068459731075</v>
       </c>
       <c r="T3">
-        <v>0.9782553224010202</v>
+        <v>0.9882375195683776</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-0.8214823756906673</v>
+        <v>-0.4107411878453336</v>
       </c>
       <c r="W3">
-        <v>0.4295055441878594</v>
+        <v>0.3326527720939297</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-2.933865627466669</v>
+        <v>-1.466932813733334</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1568,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09347192634724312</v>
+        <v>0.09537192634724312</v>
       </c>
       <c r="C4">
-        <v>548.1519649552893</v>
+        <v>530.5321409278013</v>
       </c>
       <c r="D4">
-        <v>542.8359649552892</v>
+        <v>532.0581409278012</v>
       </c>
       <c r="E4">
-        <v>-469.316</v>
+        <v>-462.474</v>
       </c>
       <c r="F4">
-        <v>13.684</v>
+        <v>20.526</v>
       </c>
       <c r="G4">
         <v>19</v>
@@ -1604,37 +1615,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M4">
-        <v>3.2266872</v>
+        <v>4.8400308</v>
       </c>
       <c r="N4">
-        <v>-7.960020533333335</v>
+        <v>-9.573364133333335</v>
       </c>
       <c r="O4">
-        <v>-2.228805749333334</v>
+        <v>-2.680541957333334</v>
       </c>
       <c r="P4">
-        <v>-5.731214784000001</v>
+        <v>-6.892822176000001</v>
       </c>
       <c r="Q4">
-        <v>87.668785216</v>
+        <v>86.50717782400001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08859068459731075</v>
+        <v>0.08903182567563353</v>
       </c>
       <c r="T4">
-        <v>0.9882375195683776</v>
+        <v>0.9984255352340309</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-0.4107411878453336</v>
+        <v>-0.2738274585635558</v>
       </c>
       <c r="W4">
-        <v>0.3326527720939297</v>
+        <v>0.3003685147292865</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-1.466932813733334</v>
+        <v>-0.9779552091555563</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1650,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09537192634724312</v>
+        <v>0.09727192634724312</v>
       </c>
       <c r="C5">
-        <v>530.5321409278013</v>
+        <v>513.3319650126948</v>
       </c>
       <c r="D5">
-        <v>532.0581409278012</v>
+        <v>521.6999650126949</v>
       </c>
       <c r="E5">
-        <v>-462.474</v>
+        <v>-455.632</v>
       </c>
       <c r="F5">
-        <v>20.526</v>
+        <v>27.368</v>
       </c>
       <c r="G5">
         <v>19</v>
@@ -1686,37 +1697,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M5">
-        <v>4.8400308</v>
+        <v>6.4533744</v>
       </c>
       <c r="N5">
-        <v>-9.573364133333335</v>
+        <v>-11.18670773333334</v>
       </c>
       <c r="O5">
-        <v>-2.680541957333334</v>
+        <v>-3.132278165333334</v>
       </c>
       <c r="P5">
-        <v>-6.892822176000001</v>
+        <v>-8.054429568000002</v>
       </c>
       <c r="Q5">
-        <v>86.50717782400001</v>
+        <v>85.345570432</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08903182567563353</v>
+        <v>0.08948215719308805</v>
       </c>
       <c r="T5">
-        <v>0.9984255352340309</v>
+        <v>1.008825801226052</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-0.2738274585635558</v>
+        <v>-0.2053705939226668</v>
       </c>
       <c r="W5">
-        <v>0.3003685147292865</v>
+        <v>0.2842263860469649</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-0.9779552091555563</v>
+        <v>-0.7334664068666672</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1732,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09727192634724312</v>
+        <v>0.09917192634724312</v>
       </c>
       <c r="C6">
-        <v>513.3319650126948</v>
+        <v>496.5273959588008</v>
       </c>
       <c r="D6">
-        <v>521.6999650126949</v>
+        <v>511.7373959588008</v>
       </c>
       <c r="E6">
-        <v>-455.632</v>
+        <v>-448.79</v>
       </c>
       <c r="F6">
-        <v>27.368</v>
+        <v>34.21</v>
       </c>
       <c r="G6">
         <v>19</v>
@@ -1768,37 +1779,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M6">
-        <v>6.4533744</v>
+        <v>8.066718</v>
       </c>
       <c r="N6">
-        <v>-11.18670773333334</v>
+        <v>-12.80005133333333</v>
       </c>
       <c r="O6">
-        <v>-3.132278165333334</v>
+        <v>-3.584014373333334</v>
       </c>
       <c r="P6">
-        <v>-8.054429568000002</v>
+        <v>-9.21603696</v>
       </c>
       <c r="Q6">
-        <v>85.345570432</v>
+        <v>84.18396304000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08948215719308805</v>
+        <v>0.08994196937406793</v>
       </c>
       <c r="T6">
-        <v>1.008825801226052</v>
+        <v>1.019445020186326</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-0.2053705939226668</v>
+        <v>-0.1642964751381334</v>
       </c>
       <c r="W6">
-        <v>0.2842263860469649</v>
+        <v>0.2745411088375719</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-0.7334664068666672</v>
+        <v>-0.5867731254933337</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1814,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09917192634724312</v>
+        <v>0.1010719263472431</v>
       </c>
       <c r="C7">
-        <v>496.5273959588008</v>
+        <v>480.096194504818</v>
       </c>
       <c r="D7">
-        <v>511.7373959588008</v>
+        <v>502.148194504818</v>
       </c>
       <c r="E7">
-        <v>-448.79</v>
+        <v>-441.948</v>
       </c>
       <c r="F7">
-        <v>34.21</v>
+        <v>41.05200000000001</v>
       </c>
       <c r="G7">
         <v>19</v>
@@ -1850,37 +1861,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M7">
-        <v>8.066718</v>
+        <v>9.680061600000002</v>
       </c>
       <c r="N7">
-        <v>-12.80005133333333</v>
+        <v>-14.41339493333334</v>
       </c>
       <c r="O7">
-        <v>-3.584014373333334</v>
+        <v>-4.035750581333335</v>
       </c>
       <c r="P7">
-        <v>-9.21603696</v>
+        <v>-10.377644352</v>
       </c>
       <c r="Q7">
-        <v>84.18396304000001</v>
+        <v>83.022355648</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08994196937406793</v>
+        <v>0.09041156479294099</v>
       </c>
       <c r="T7">
-        <v>1.019445020186326</v>
+        <v>1.030290179975542</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-0.1642964751381334</v>
+        <v>-0.1369137292817779</v>
       </c>
       <c r="W7">
-        <v>0.2745411088375719</v>
+        <v>0.2680842573646433</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-0.5867731254933337</v>
+        <v>-0.4889776045777781</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1896,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1010719263472431</v>
+        <v>0.1029719263472431</v>
       </c>
       <c r="C8">
-        <v>480.0961945048181</v>
+        <v>464.0177576516878</v>
       </c>
       <c r="D8">
-        <v>502.148194504818</v>
+        <v>492.9117576516878</v>
       </c>
       <c r="E8">
-        <v>-441.948</v>
+        <v>-435.106</v>
       </c>
       <c r="F8">
-        <v>41.052</v>
+        <v>47.894</v>
       </c>
       <c r="G8">
         <v>19</v>
@@ -1932,37 +1943,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M8">
-        <v>9.6800616</v>
+        <v>11.2934052</v>
       </c>
       <c r="N8">
-        <v>-14.41339493333333</v>
+        <v>-16.02673853333334</v>
       </c>
       <c r="O8">
-        <v>-4.035750581333334</v>
+        <v>-4.487486789333334</v>
       </c>
       <c r="P8">
-        <v>-10.377644352</v>
+        <v>-11.539251744</v>
       </c>
       <c r="Q8">
-        <v>83.022355648</v>
+        <v>81.86074825600001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09041156479294099</v>
+        <v>0.09089125903802638</v>
       </c>
       <c r="T8">
-        <v>1.030290179975542</v>
+        <v>1.041368569007538</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-0.1369137292817779</v>
+        <v>-0.1173546250986667</v>
       </c>
       <c r="W8">
-        <v>0.2680842573646433</v>
+        <v>0.2634722205982656</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-0.4889776045777781</v>
+        <v>-0.4191236610666671</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1978,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1029719263472431</v>
+        <v>0.1048719263472431</v>
       </c>
       <c r="C9">
-        <v>464.0177576516878</v>
+        <v>448.2729708948278</v>
       </c>
       <c r="D9">
-        <v>492.9117576516878</v>
+        <v>484.0089708948278</v>
       </c>
       <c r="E9">
-        <v>-435.106</v>
+        <v>-428.264</v>
       </c>
       <c r="F9">
-        <v>47.89400000000001</v>
+        <v>54.736</v>
       </c>
       <c r="G9">
         <v>19</v>
@@ -2014,37 +2025,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M9">
-        <v>11.2934052</v>
+        <v>12.9067488</v>
       </c>
       <c r="N9">
-        <v>-16.02673853333334</v>
+        <v>-17.64008213333334</v>
       </c>
       <c r="O9">
-        <v>-4.487486789333334</v>
+        <v>-4.939222997333335</v>
       </c>
       <c r="P9">
-        <v>-11.539251744</v>
+        <v>-12.700859136</v>
       </c>
       <c r="Q9">
-        <v>81.86074825600001</v>
+        <v>80.699140864</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09089125903802638</v>
+        <v>0.0913813814188745</v>
       </c>
       <c r="T9">
-        <v>1.041368569007538</v>
+        <v>1.052687792583707</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-0.1173546250986667</v>
+        <v>-0.1026852969613334</v>
       </c>
       <c r="W9">
-        <v>0.2634722205982656</v>
+        <v>0.2600131930234824</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.4191236610666669</v>
+        <v>-0.3667332034333337</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2060,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1048719263472431</v>
+        <v>0.1067719263472431</v>
       </c>
       <c r="C10">
-        <v>448.2729708948278</v>
+        <v>432.844076185822</v>
       </c>
       <c r="D10">
-        <v>484.0089708948278</v>
+        <v>475.422076185822</v>
       </c>
       <c r="E10">
-        <v>-428.264</v>
+        <v>-421.422</v>
       </c>
       <c r="F10">
-        <v>54.736</v>
+        <v>61.578</v>
       </c>
       <c r="G10">
         <v>19</v>
@@ -2096,37 +2107,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M10">
-        <v>12.9067488</v>
+        <v>14.5200924</v>
       </c>
       <c r="N10">
-        <v>-17.64008213333334</v>
+        <v>-19.25342573333334</v>
       </c>
       <c r="O10">
-        <v>-4.939222997333335</v>
+        <v>-5.390959205333335</v>
       </c>
       <c r="P10">
-        <v>-12.700859136</v>
+        <v>-13.862466528</v>
       </c>
       <c r="Q10">
-        <v>80.699140864</v>
+        <v>79.53753347200001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0913813814188745</v>
+        <v>0.0918822757201808</v>
       </c>
       <c r="T10">
-        <v>1.052687792583707</v>
+        <v>1.064255790304407</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-0.1026852969613334</v>
+        <v>-0.09127581952118524</v>
       </c>
       <c r="W10">
-        <v>0.2600131930234824</v>
+        <v>0.2573228382430955</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.3667332034333337</v>
+        <v>-0.3259850697185189</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2142,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1067719263472431</v>
+        <v>0.1086719263472431</v>
       </c>
       <c r="C11">
-        <v>432.844076185822</v>
+        <v>417.7145537042026</v>
       </c>
       <c r="D11">
-        <v>475.422076185822</v>
+        <v>467.1345537042026</v>
       </c>
       <c r="E11">
-        <v>-421.422</v>
+        <v>-414.58</v>
       </c>
       <c r="F11">
-        <v>61.578</v>
+        <v>68.42</v>
       </c>
       <c r="G11">
         <v>19</v>
@@ -2178,37 +2189,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M11">
-        <v>14.5200924</v>
+        <v>16.133436</v>
       </c>
       <c r="N11">
-        <v>-19.25342573333334</v>
+        <v>-20.86676933333333</v>
       </c>
       <c r="O11">
-        <v>-5.390959205333335</v>
+        <v>-5.842695413333334</v>
       </c>
       <c r="P11">
-        <v>-13.862466528</v>
+        <v>-15.02407392</v>
       </c>
       <c r="Q11">
-        <v>79.53753347200001</v>
+        <v>78.37592608</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0918822757201808</v>
+        <v>0.09239430100596058</v>
       </c>
       <c r="T11">
-        <v>1.064255790304407</v>
+        <v>1.076080854641122</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.09127581952118524</v>
+        <v>-0.08214823756906672</v>
       </c>
       <c r="W11">
-        <v>0.2573228382430955</v>
+        <v>0.2551705544187859</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.3259850697185189</v>
+        <v>-0.293386562746667</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2224,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1086719263472431</v>
+        <v>0.1105719263472431</v>
       </c>
       <c r="C12">
-        <v>417.7145537042026</v>
+        <v>402.8690157830408</v>
       </c>
       <c r="D12">
-        <v>467.1345537042026</v>
+        <v>459.1310157830408</v>
       </c>
       <c r="E12">
-        <v>-414.58</v>
+        <v>-407.738</v>
       </c>
       <c r="F12">
-        <v>68.42</v>
+        <v>75.262</v>
       </c>
       <c r="G12">
         <v>19</v>
@@ -2260,37 +2271,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M12">
-        <v>16.133436</v>
+        <v>17.7467796</v>
       </c>
       <c r="N12">
-        <v>-20.86676933333333</v>
+        <v>-22.48011293333333</v>
       </c>
       <c r="O12">
-        <v>-5.842695413333334</v>
+        <v>-6.294431621333334</v>
       </c>
       <c r="P12">
-        <v>-15.02407392</v>
+        <v>-16.185681312</v>
       </c>
       <c r="Q12">
-        <v>78.37592608</v>
+        <v>77.21431868800001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09239430100596058</v>
+        <v>0.09291783247793767</v>
       </c>
       <c r="T12">
-        <v>1.076080854641122</v>
+        <v>1.088171650760685</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.08214823756906672</v>
+        <v>-0.07468021597187885</v>
       </c>
       <c r="W12">
-        <v>0.2551705544187859</v>
+        <v>0.253409594926169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.293386562746667</v>
+        <v>-0.2667150570424244</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2306,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1105719263472431</v>
+        <v>0.1124719263472431</v>
       </c>
       <c r="C13">
-        <v>402.8690157830408</v>
+        <v>388.2931115552601</v>
       </c>
       <c r="D13">
-        <v>459.1310157830408</v>
+        <v>451.39711155526</v>
       </c>
       <c r="E13">
-        <v>-407.738</v>
+        <v>-400.896</v>
       </c>
       <c r="F13">
-        <v>75.262</v>
+        <v>82.104</v>
       </c>
       <c r="G13">
         <v>19</v>
@@ -2342,37 +2353,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M13">
-        <v>17.7467796</v>
+        <v>19.3601232</v>
       </c>
       <c r="N13">
-        <v>-22.48011293333333</v>
+        <v>-24.09345653333333</v>
       </c>
       <c r="O13">
-        <v>-6.294431621333334</v>
+        <v>-6.746167829333334</v>
       </c>
       <c r="P13">
-        <v>-16.185681312</v>
+        <v>-17.347288704</v>
       </c>
       <c r="Q13">
-        <v>77.21431868800001</v>
+        <v>76.05271129600001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09291783247793767</v>
+        <v>0.09345326239245969</v>
       </c>
       <c r="T13">
-        <v>1.088171650760685</v>
+        <v>1.100537237701148</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.07468021597187885</v>
+        <v>-0.06845686464088895</v>
       </c>
       <c r="W13">
-        <v>0.253409594926169</v>
+        <v>0.2519421286823216</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.2667150570424244</v>
+        <v>-0.2444888022888891</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2388,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1124719263472431</v>
+        <v>0.1143719263472431</v>
       </c>
       <c r="C14">
-        <v>388.2931115552601</v>
+        <v>373.9734410775031</v>
       </c>
       <c r="D14">
-        <v>451.39711155526</v>
+        <v>443.9194410775031</v>
       </c>
       <c r="E14">
-        <v>-400.896</v>
+        <v>-394.054</v>
       </c>
       <c r="F14">
-        <v>82.104</v>
+        <v>88.94600000000001</v>
       </c>
       <c r="G14">
         <v>19</v>
@@ -2424,37 +2435,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M14">
-        <v>19.3601232</v>
+        <v>20.9734668</v>
       </c>
       <c r="N14">
-        <v>-24.09345653333333</v>
+        <v>-25.70680013333334</v>
       </c>
       <c r="O14">
-        <v>-6.746167829333334</v>
+        <v>-7.197904037333336</v>
       </c>
       <c r="P14">
-        <v>-17.347288704</v>
+        <v>-18.508896096</v>
       </c>
       <c r="Q14">
-        <v>76.05271129600001</v>
+        <v>74.891103904</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09345326239245969</v>
+        <v>0.09400100104064889</v>
       </c>
       <c r="T14">
-        <v>1.100537237701148</v>
+        <v>1.113187091008057</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.06845686464088895</v>
+        <v>-0.06319095197620517</v>
       </c>
       <c r="W14">
-        <v>0.2519421286823216</v>
+        <v>0.2507004264759892</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.2444888022888891</v>
+        <v>-0.2256819713435898</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2470,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1143719263472431</v>
+        <v>0.1162719263472431</v>
       </c>
       <c r="C15">
-        <v>373.9734410775031</v>
+        <v>359.8974778504527</v>
       </c>
       <c r="D15">
-        <v>443.9194410775031</v>
+        <v>436.6854778504527</v>
       </c>
       <c r="E15">
-        <v>-394.054</v>
+        <v>-387.212</v>
       </c>
       <c r="F15">
-        <v>88.94600000000001</v>
+        <v>95.78800000000001</v>
       </c>
       <c r="G15">
         <v>19</v>
@@ -2506,37 +2517,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M15">
-        <v>20.9734668</v>
+        <v>22.5868104</v>
       </c>
       <c r="N15">
-        <v>-25.70680013333334</v>
+        <v>-27.32014373333334</v>
       </c>
       <c r="O15">
-        <v>-7.197904037333336</v>
+        <v>-7.649640245333336</v>
       </c>
       <c r="P15">
-        <v>-18.508896096</v>
+        <v>-19.670503488</v>
       </c>
       <c r="Q15">
-        <v>74.891103904</v>
+        <v>73.729496512</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09400100104064889</v>
+        <v>0.09456147779693549</v>
       </c>
       <c r="T15">
-        <v>1.113187091008057</v>
+        <v>1.126131126950012</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.06319095197620517</v>
+        <v>-0.05867731254933337</v>
       </c>
       <c r="W15">
-        <v>0.2507004264759892</v>
+        <v>0.2496361102991328</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.2256819713435898</v>
+        <v>-0.2095618305333335</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2552,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1162719263472431</v>
+        <v>0.1181719263472431</v>
       </c>
       <c r="C16">
-        <v>359.8974778504527</v>
+        <v>346.0534987931813</v>
       </c>
       <c r="D16">
-        <v>436.6854778504527</v>
+        <v>429.6834987931814</v>
       </c>
       <c r="E16">
-        <v>-387.212</v>
+        <v>-380.37</v>
       </c>
       <c r="F16">
-        <v>95.78800000000001</v>
+        <v>102.63</v>
       </c>
       <c r="G16">
         <v>19</v>
@@ -2588,37 +2599,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M16">
-        <v>22.5868104</v>
+        <v>24.20015400000001</v>
       </c>
       <c r="N16">
-        <v>-27.32014373333334</v>
+        <v>-28.93348733333334</v>
       </c>
       <c r="O16">
-        <v>-7.649640245333336</v>
+        <v>-8.101376453333337</v>
       </c>
       <c r="P16">
-        <v>-19.670503488</v>
+        <v>-20.83211088000001</v>
       </c>
       <c r="Q16">
-        <v>73.729496512</v>
+        <v>72.56788912</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09456147779693549</v>
+        <v>0.09513514224160532</v>
       </c>
       <c r="T16">
-        <v>1.126131126950012</v>
+        <v>1.139379728443541</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.05867731254933337</v>
+        <v>-0.05476549171271113</v>
       </c>
       <c r="W16">
-        <v>0.2496361102991328</v>
+        <v>0.2487137029458573</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.2095618305333335</v>
+        <v>-0.1955910418311111</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2634,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1181719263472431</v>
+        <v>0.1200719263472431</v>
       </c>
       <c r="C17">
-        <v>346.0534987931815</v>
+        <v>332.4305208480902</v>
       </c>
       <c r="D17">
-        <v>429.6834987931815</v>
+        <v>422.9025208480902</v>
       </c>
       <c r="E17">
-        <v>-380.37</v>
+        <v>-373.528</v>
       </c>
       <c r="F17">
-        <v>102.63</v>
+        <v>109.472</v>
       </c>
       <c r="G17">
         <v>19</v>
@@ -2670,37 +2681,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M17">
-        <v>24.200154</v>
+        <v>25.8134976</v>
       </c>
       <c r="N17">
-        <v>-28.93348733333334</v>
+        <v>-30.54683093333334</v>
       </c>
       <c r="O17">
-        <v>-8.101376453333335</v>
+        <v>-8.553112661333335</v>
       </c>
       <c r="P17">
-        <v>-20.83211088</v>
+        <v>-21.993718272</v>
       </c>
       <c r="Q17">
-        <v>72.56788912</v>
+        <v>71.40628172800001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09513514224160532</v>
+        <v>0.09572246536352921</v>
       </c>
       <c r="T17">
-        <v>1.139379728443541</v>
+        <v>1.152943772829774</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.05476549171271114</v>
+        <v>-0.05134264848066671</v>
       </c>
       <c r="W17">
-        <v>0.2487137029458573</v>
+        <v>0.2479065965117412</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.1955910418311113</v>
+        <v>-0.1833666017166669</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2716,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1200719263472431</v>
+        <v>0.1219719263472431</v>
       </c>
       <c r="C18">
-        <v>332.4305208480902</v>
+        <v>319.0182434953379</v>
       </c>
       <c r="D18">
-        <v>422.9025208480902</v>
+        <v>416.3322434953379</v>
       </c>
       <c r="E18">
-        <v>-373.528</v>
+        <v>-366.686</v>
       </c>
       <c r="F18">
-        <v>109.472</v>
+        <v>116.314</v>
       </c>
       <c r="G18">
         <v>19</v>
@@ -2752,37 +2763,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M18">
-        <v>25.8134976</v>
+        <v>27.42684120000001</v>
       </c>
       <c r="N18">
-        <v>-30.54683093333334</v>
+        <v>-32.16017453333334</v>
       </c>
       <c r="O18">
-        <v>-8.553112661333335</v>
+        <v>-9.004848869333337</v>
       </c>
       <c r="P18">
-        <v>-21.993718272</v>
+        <v>-23.155325664</v>
       </c>
       <c r="Q18">
-        <v>71.40628172800001</v>
+        <v>70.244674336</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09572246536352921</v>
+        <v>0.09632394084983679</v>
       </c>
       <c r="T18">
-        <v>1.152943772829774</v>
+        <v>1.166834661659048</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.05134264848066671</v>
+        <v>-0.04832249268768631</v>
       </c>
       <c r="W18">
-        <v>0.2479065965117412</v>
+        <v>0.2471944437757565</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.1833666017166669</v>
+        <v>-0.172580331027451</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2798,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1219719263472431</v>
+        <v>0.1238719263472431</v>
       </c>
       <c r="C19">
-        <v>319.0182434953379</v>
+        <v>305.8069965439192</v>
       </c>
       <c r="D19">
-        <v>416.3322434953379</v>
+        <v>409.9629965439192</v>
       </c>
       <c r="E19">
-        <v>-366.686</v>
+        <v>-359.844</v>
       </c>
       <c r="F19">
-        <v>116.314</v>
+        <v>123.156</v>
       </c>
       <c r="G19">
         <v>19</v>
@@ -2834,37 +2845,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M19">
-        <v>27.42684120000001</v>
+        <v>29.04018480000001</v>
       </c>
       <c r="N19">
-        <v>-32.16017453333334</v>
+        <v>-33.77351813333334</v>
       </c>
       <c r="O19">
-        <v>-9.004848869333337</v>
+        <v>-9.456585077333337</v>
       </c>
       <c r="P19">
-        <v>-23.155325664</v>
+        <v>-24.316933056</v>
       </c>
       <c r="Q19">
-        <v>70.244674336</v>
+        <v>69.083066944</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09632394084983679</v>
+        <v>0.09694008646995675</v>
       </c>
       <c r="T19">
-        <v>1.166834661659048</v>
+        <v>1.18106435265489</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.04832249268768631</v>
+        <v>-0.04563790976059262</v>
       </c>
       <c r="W19">
-        <v>0.2471944437757565</v>
+        <v>0.2465614191215477</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.172580331027451</v>
+        <v>-0.1629925348592594</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2880,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1238719263472431</v>
+        <v>0.1257719263472431</v>
       </c>
       <c r="C20">
-        <v>305.8069965439192</v>
+        <v>292.7876926428327</v>
       </c>
       <c r="D20">
-        <v>409.9629965439192</v>
+        <v>403.7856926428327</v>
       </c>
       <c r="E20">
-        <v>-359.844</v>
+        <v>-353.002</v>
       </c>
       <c r="F20">
-        <v>123.156</v>
+        <v>129.998</v>
       </c>
       <c r="G20">
         <v>19</v>
@@ -2916,37 +2927,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M20">
-        <v>29.0401848</v>
+        <v>30.65352840000001</v>
       </c>
       <c r="N20">
-        <v>-33.77351813333334</v>
+        <v>-35.38686173333334</v>
       </c>
       <c r="O20">
-        <v>-9.456585077333337</v>
+        <v>-9.908321285333336</v>
       </c>
       <c r="P20">
-        <v>-24.316933056</v>
+        <v>-25.478540448</v>
       </c>
       <c r="Q20">
-        <v>69.083066944</v>
+        <v>67.921459552</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09694008646995673</v>
+        <v>0.09757144556217842</v>
       </c>
       <c r="T20">
-        <v>1.18106435265489</v>
+        <v>1.195645394045691</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.04563790976059262</v>
+        <v>-0.04323591451003512</v>
       </c>
       <c r="W20">
-        <v>0.2465614191215477</v>
+        <v>0.2459950286414663</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.1629925348592596</v>
+        <v>-0.1544139803929825</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2962,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1257719263472431</v>
+        <v>0.1276719263472431</v>
       </c>
       <c r="C21">
-        <v>292.7876926428327</v>
+        <v>279.9517840218743</v>
       </c>
       <c r="D21">
-        <v>403.7856926428327</v>
+        <v>397.7917840218743</v>
       </c>
       <c r="E21">
-        <v>-353.002</v>
+        <v>-346.16</v>
       </c>
       <c r="F21">
-        <v>129.998</v>
+        <v>136.84</v>
       </c>
       <c r="G21">
         <v>19</v>
@@ -2998,37 +3009,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M21">
-        <v>30.65352840000001</v>
+        <v>32.266872</v>
       </c>
       <c r="N21">
-        <v>-35.38686173333334</v>
+        <v>-37.00020533333333</v>
       </c>
       <c r="O21">
-        <v>-9.908321285333336</v>
+        <v>-10.36005749333333</v>
       </c>
       <c r="P21">
-        <v>-25.478540448</v>
+        <v>-26.64014784</v>
       </c>
       <c r="Q21">
-        <v>67.921459552</v>
+        <v>66.75985216000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09757144556217842</v>
+        <v>0.09821858863170566</v>
       </c>
       <c r="T21">
-        <v>1.195645394045691</v>
+        <v>1.210590961471262</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.04323591451003512</v>
+        <v>-0.04107411878453336</v>
       </c>
       <c r="W21">
-        <v>0.2459950286414663</v>
+        <v>0.245485277209393</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.1544139803929825</v>
+        <v>-0.1466932813733335</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3044,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1276719263472431</v>
+        <v>0.1295719263472431</v>
       </c>
       <c r="C22">
-        <v>279.9517840218743</v>
+        <v>267.2912230289853</v>
       </c>
       <c r="D22">
-        <v>397.7917840218743</v>
+        <v>391.9732230289853</v>
       </c>
       <c r="E22">
-        <v>-346.16</v>
+        <v>-339.318</v>
       </c>
       <c r="F22">
-        <v>136.84</v>
+        <v>143.682</v>
       </c>
       <c r="G22">
         <v>19</v>
@@ -3080,37 +3091,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M22">
-        <v>32.266872</v>
+        <v>33.88021560000001</v>
       </c>
       <c r="N22">
-        <v>-37.00020533333333</v>
+        <v>-38.61354893333334</v>
       </c>
       <c r="O22">
-        <v>-10.36005749333333</v>
+        <v>-10.81179370133334</v>
       </c>
       <c r="P22">
-        <v>-26.64014784</v>
+        <v>-27.801755232</v>
       </c>
       <c r="Q22">
-        <v>66.75985216000001</v>
+        <v>65.598244768</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09821858863170566</v>
+        <v>0.09888211507008168</v>
       </c>
       <c r="T22">
-        <v>1.210590961471262</v>
+        <v>1.225914897692418</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.04107411878453336</v>
+        <v>-0.03911820836622224</v>
       </c>
       <c r="W22">
-        <v>0.245485277209393</v>
+        <v>0.2450240735327552</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.1466932813733335</v>
+        <v>-0.1397078870222224</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3126,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1295719263472431</v>
+        <v>0.1314719263472431</v>
       </c>
       <c r="C23">
-        <v>267.2912230289853</v>
+        <v>254.7984260810279</v>
       </c>
       <c r="D23">
-        <v>391.9732230289853</v>
+        <v>386.3224260810279</v>
       </c>
       <c r="E23">
-        <v>-339.318</v>
+        <v>-332.476</v>
       </c>
       <c r="F23">
-        <v>143.682</v>
+        <v>150.524</v>
       </c>
       <c r="G23">
         <v>19</v>
@@ -3162,37 +3173,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M23">
-        <v>33.88021560000001</v>
+        <v>35.4935592</v>
       </c>
       <c r="N23">
-        <v>-38.61354893333334</v>
+        <v>-40.22689253333333</v>
       </c>
       <c r="O23">
-        <v>-10.81179370133334</v>
+        <v>-11.26352990933333</v>
       </c>
       <c r="P23">
-        <v>-27.801755232</v>
+        <v>-28.963362624</v>
       </c>
       <c r="Q23">
-        <v>65.598244768</v>
+        <v>64.43663737600001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09888211507008168</v>
+        <v>0.09956265500687761</v>
       </c>
       <c r="T23">
-        <v>1.225914897692418</v>
+        <v>1.241631755355141</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.03911820836622224</v>
+        <v>-0.03734010798593942</v>
       </c>
       <c r="W23">
-        <v>0.2450240735327552</v>
+        <v>0.2446047974630845</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.1397078870222224</v>
+        <v>-0.1333575285212123</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3208,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1314719263472431</v>
+        <v>0.1333719263472431</v>
       </c>
       <c r="C24">
-        <v>254.7984260810279</v>
+        <v>242.4662406884233</v>
       </c>
       <c r="D24">
-        <v>386.3224260810279</v>
+        <v>380.8322406884233</v>
       </c>
       <c r="E24">
-        <v>-332.476</v>
+        <v>-325.634</v>
       </c>
       <c r="F24">
-        <v>150.524</v>
+        <v>157.366</v>
       </c>
       <c r="G24">
         <v>19</v>
@@ -3244,37 +3255,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M24">
-        <v>35.4935592</v>
+        <v>37.10690280000001</v>
       </c>
       <c r="N24">
-        <v>-40.22689253333333</v>
+        <v>-41.84023613333334</v>
       </c>
       <c r="O24">
-        <v>-11.26352990933333</v>
+        <v>-11.71526611733334</v>
       </c>
       <c r="P24">
-        <v>-28.963362624</v>
+        <v>-30.12497001600001</v>
       </c>
       <c r="Q24">
-        <v>64.43663737600001</v>
+        <v>63.275029984</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09956265500687761</v>
+        <v>0.1002608713056682</v>
       </c>
       <c r="T24">
-        <v>1.241631755355141</v>
+        <v>1.257756843087026</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.03734010798593942</v>
+        <v>-0.03571662503002901</v>
       </c>
       <c r="W24">
-        <v>0.2446047974630845</v>
+        <v>0.2442219801820808</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.1333575285212123</v>
+        <v>-0.1275593751072464</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3290,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1333719263472431</v>
+        <v>0.1352719263472431</v>
       </c>
       <c r="C25">
-        <v>242.4662406884233</v>
+        <v>230.2879152521473</v>
       </c>
       <c r="D25">
-        <v>380.8322406884233</v>
+        <v>375.4959152521473</v>
       </c>
       <c r="E25">
-        <v>-325.634</v>
+        <v>-318.792</v>
       </c>
       <c r="F25">
-        <v>157.366</v>
+        <v>164.208</v>
       </c>
       <c r="G25">
         <v>19</v>
@@ -3326,37 +3337,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M25">
-        <v>37.10690280000001</v>
+        <v>38.72024640000001</v>
       </c>
       <c r="N25">
-        <v>-41.84023613333334</v>
+        <v>-43.45357973333334</v>
       </c>
       <c r="O25">
-        <v>-11.71526611733334</v>
+        <v>-12.16700232533334</v>
       </c>
       <c r="P25">
-        <v>-30.12497001600001</v>
+        <v>-31.28657740800001</v>
       </c>
       <c r="Q25">
-        <v>63.275029984</v>
+        <v>62.113422592</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1002608713056682</v>
+        <v>0.1009774617175849</v>
       </c>
       <c r="T25">
-        <v>1.257756843087026</v>
+        <v>1.274306275232908</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.03571662503002901</v>
+        <v>-0.03422843232044447</v>
       </c>
       <c r="W25">
-        <v>0.2442219801820808</v>
+        <v>0.2438710643411608</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.1275593751072464</v>
+        <v>-0.1222444011444446</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3372,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1352719263472431</v>
+        <v>0.1371719263472431</v>
       </c>
       <c r="C26">
-        <v>230.2879152521473</v>
+        <v>218.257071364914</v>
       </c>
       <c r="D26">
-        <v>375.4959152521473</v>
+        <v>370.307071364914</v>
       </c>
       <c r="E26">
-        <v>-318.792</v>
+        <v>-311.95</v>
       </c>
       <c r="F26">
-        <v>164.208</v>
+        <v>171.05</v>
       </c>
       <c r="G26">
         <v>19</v>
@@ -3408,37 +3419,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M26">
-        <v>38.7202464</v>
+        <v>40.33359</v>
       </c>
       <c r="N26">
-        <v>-43.45357973333333</v>
+        <v>-45.06692333333334</v>
       </c>
       <c r="O26">
-        <v>-12.16700232533334</v>
+        <v>-12.61873853333334</v>
       </c>
       <c r="P26">
-        <v>-31.286577408</v>
+        <v>-32.4481848</v>
       </c>
       <c r="Q26">
-        <v>62.11342259200001</v>
+        <v>60.95181520000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1009774617175849</v>
+        <v>0.1017131612071527</v>
       </c>
       <c r="T26">
-        <v>1.274306275232908</v>
+        <v>1.291297025569347</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.03422843232044447</v>
+        <v>-0.03285929502762669</v>
       </c>
       <c r="W26">
-        <v>0.2438710643411608</v>
+        <v>0.2435482217675144</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.1222444011444446</v>
+        <v>-0.1173546250986668</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3454,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1371719263472431</v>
+        <v>0.1390719263472431</v>
       </c>
       <c r="C27">
-        <v>218.257071364914</v>
+        <v>206.3676783776167</v>
       </c>
       <c r="D27">
-        <v>370.307071364914</v>
+        <v>365.2596783776167</v>
       </c>
       <c r="E27">
-        <v>-311.95</v>
+        <v>-305.1079999999999</v>
       </c>
       <c r="F27">
-        <v>171.05</v>
+        <v>177.892</v>
       </c>
       <c r="G27">
         <v>19</v>
@@ -3490,37 +3501,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M27">
-        <v>40.33359</v>
+        <v>41.94693360000001</v>
       </c>
       <c r="N27">
-        <v>-45.06692333333334</v>
+        <v>-46.68026693333334</v>
       </c>
       <c r="O27">
-        <v>-12.61873853333334</v>
+        <v>-13.07047474133334</v>
       </c>
       <c r="P27">
-        <v>-32.4481848</v>
+        <v>-33.60979219200001</v>
       </c>
       <c r="Q27">
-        <v>60.95181520000001</v>
+        <v>59.790207808</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1017131612071527</v>
+        <v>0.1024687444667088</v>
       </c>
       <c r="T27">
-        <v>1.291297025569347</v>
+        <v>1.308746985374338</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.03285929502762669</v>
+        <v>-0.03159547598810258</v>
       </c>
       <c r="W27">
-        <v>0.2435482217675144</v>
+        <v>0.2432502132379946</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.1173546250986668</v>
+        <v>-0.1128409856717949</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3536,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1390719263472431</v>
+        <v>0.1409719263472431</v>
       </c>
       <c r="C28">
-        <v>206.3676783776167</v>
+        <v>194.6140300177993</v>
       </c>
       <c r="D28">
-        <v>365.2596783776167</v>
+        <v>360.3480300177994</v>
       </c>
       <c r="E28">
-        <v>-305.1079999999999</v>
+        <v>-298.266</v>
       </c>
       <c r="F28">
-        <v>177.892</v>
+        <v>184.734</v>
       </c>
       <c r="G28">
         <v>19</v>
@@ -3572,37 +3583,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M28">
-        <v>41.94693360000001</v>
+        <v>43.56027720000001</v>
       </c>
       <c r="N28">
-        <v>-46.68026693333334</v>
+        <v>-48.29361053333334</v>
       </c>
       <c r="O28">
-        <v>-13.07047474133334</v>
+        <v>-13.52221094933334</v>
       </c>
       <c r="P28">
-        <v>-33.60979219200001</v>
+        <v>-34.77139958400001</v>
       </c>
       <c r="Q28">
-        <v>59.790207808</v>
+        <v>58.628600416</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1024687444667088</v>
+        <v>0.1032450286374857</v>
       </c>
       <c r="T28">
-        <v>1.308746985374338</v>
+        <v>1.326675026269877</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.03159547598810258</v>
+        <v>-0.03042527317372841</v>
       </c>
       <c r="W28">
-        <v>0.2432502132379946</v>
+        <v>0.2429742794143652</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.1128409856717949</v>
+        <v>-0.108661689906173</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3618,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1409719263472431</v>
+        <v>0.1428719263472431</v>
       </c>
       <c r="C29">
-        <v>194.6140300177993</v>
+        <v>182.990722869567</v>
       </c>
       <c r="D29">
-        <v>360.3480300177994</v>
+        <v>355.566722869567</v>
       </c>
       <c r="E29">
-        <v>-298.266</v>
+        <v>-291.424</v>
       </c>
       <c r="F29">
-        <v>184.734</v>
+        <v>191.576</v>
       </c>
       <c r="G29">
         <v>19</v>
@@ -3654,37 +3665,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M29">
-        <v>43.56027720000001</v>
+        <v>45.17362080000001</v>
       </c>
       <c r="N29">
-        <v>-48.29361053333334</v>
+        <v>-49.90695413333334</v>
       </c>
       <c r="O29">
-        <v>-13.52221094933334</v>
+        <v>-13.97394715733334</v>
       </c>
       <c r="P29">
-        <v>-34.77139958400001</v>
+        <v>-35.933006976</v>
       </c>
       <c r="Q29">
-        <v>58.628600416</v>
+        <v>57.466993024</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1032450286374857</v>
+        <v>0.1040428762574507</v>
       </c>
       <c r="T29">
-        <v>1.326675026269877</v>
+        <v>1.345101068301403</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.03042527317372841</v>
+        <v>-0.02933865627466668</v>
       </c>
       <c r="W29">
-        <v>0.2429742794143652</v>
+        <v>0.2427180551495664</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.108661689906173</v>
+        <v>-0.1047809152666668</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3700,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1428719263472431</v>
+        <v>0.1447719263472431</v>
       </c>
       <c r="C30">
-        <v>182.990722869567</v>
+        <v>171.4926365443076</v>
       </c>
       <c r="D30">
-        <v>355.566722869567</v>
+        <v>350.9106365443076</v>
       </c>
       <c r="E30">
-        <v>-291.424</v>
+        <v>-284.582</v>
       </c>
       <c r="F30">
-        <v>191.576</v>
+        <v>198.418</v>
       </c>
       <c r="G30">
         <v>19</v>
@@ -3736,37 +3747,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M30">
-        <v>45.17362080000001</v>
+        <v>46.78696440000001</v>
       </c>
       <c r="N30">
-        <v>-49.90695413333334</v>
+        <v>-51.52029773333334</v>
       </c>
       <c r="O30">
-        <v>-13.97394715733334</v>
+        <v>-14.42568336533334</v>
       </c>
       <c r="P30">
-        <v>-35.933006976</v>
+        <v>-37.09461436800001</v>
       </c>
       <c r="Q30">
-        <v>57.466993024</v>
+        <v>56.305385632</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1040428762574507</v>
+        <v>0.1048631984582599</v>
       </c>
       <c r="T30">
-        <v>1.345101068301403</v>
+        <v>1.364046153770437</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.02933865627466668</v>
+        <v>-0.02832697847209197</v>
       </c>
       <c r="W30">
-        <v>0.2427180551495664</v>
+        <v>0.2424795015237193</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.1047809152666668</v>
+        <v>-0.1011677802574713</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3782,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1447719263472431</v>
+        <v>0.1466719263472431</v>
       </c>
       <c r="C31">
-        <v>171.4926365443076</v>
+        <v>160.1149153892422</v>
       </c>
       <c r="D31">
-        <v>350.9106365443076</v>
+        <v>346.3749153892422</v>
       </c>
       <c r="E31">
-        <v>-284.582</v>
+        <v>-277.74</v>
       </c>
       <c r="F31">
-        <v>198.418</v>
+        <v>205.26</v>
       </c>
       <c r="G31">
         <v>19</v>
@@ -3818,37 +3829,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M31">
-        <v>46.7869644</v>
+        <v>48.40030800000001</v>
       </c>
       <c r="N31">
-        <v>-51.52029773333334</v>
+        <v>-53.13364133333334</v>
       </c>
       <c r="O31">
-        <v>-14.42568336533334</v>
+        <v>-14.87741957333334</v>
       </c>
       <c r="P31">
-        <v>-37.094614368</v>
+        <v>-38.25622176</v>
       </c>
       <c r="Q31">
-        <v>56.305385632</v>
+        <v>55.14377824</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1048631984582599</v>
+        <v>0.105706958436235</v>
       </c>
       <c r="T31">
-        <v>1.364046153770436</v>
+        <v>1.383532527395729</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.02832697847209198</v>
+        <v>-0.02738274585635557</v>
       </c>
       <c r="W31">
-        <v>0.2424795015237193</v>
+        <v>0.2422568514729287</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.1011677802574713</v>
+        <v>-0.09779552091555566</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3864,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1466719263472431</v>
+        <v>0.1485719263472431</v>
       </c>
       <c r="C32">
-        <v>160.1149153892422</v>
+        <v>148.8529515964392</v>
       </c>
       <c r="D32">
-        <v>346.3749153892422</v>
+        <v>341.9549515964392</v>
       </c>
       <c r="E32">
-        <v>-277.74</v>
+        <v>-270.898</v>
       </c>
       <c r="F32">
-        <v>205.26</v>
+        <v>212.102</v>
       </c>
       <c r="G32">
         <v>19</v>
@@ -3900,37 +3911,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M32">
-        <v>48.40030800000001</v>
+        <v>50.0136516</v>
       </c>
       <c r="N32">
-        <v>-53.13364133333334</v>
+        <v>-54.74698493333334</v>
       </c>
       <c r="O32">
-        <v>-14.87741957333334</v>
+        <v>-15.32915578133334</v>
       </c>
       <c r="P32">
-        <v>-38.25622176</v>
+        <v>-39.417829152</v>
       </c>
       <c r="Q32">
-        <v>55.14377824</v>
+        <v>53.982170848</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.105706958436235</v>
+        <v>0.106575175225166</v>
       </c>
       <c r="T32">
-        <v>1.383532527395729</v>
+        <v>1.403583723444942</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.02738274585635557</v>
+        <v>-0.0264994314738925</v>
       </c>
       <c r="W32">
-        <v>0.2422568514729287</v>
+        <v>0.2420485659415438</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.09779552091555566</v>
+        <v>-0.0946408266924732</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3946,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1485719263472431</v>
+        <v>0.1504719263472431</v>
       </c>
       <c r="C33">
-        <v>148.8529515964392</v>
+        <v>137.7023695887708</v>
       </c>
       <c r="D33">
-        <v>341.9549515964392</v>
+        <v>337.6463695887708</v>
       </c>
       <c r="E33">
-        <v>-270.898</v>
+        <v>-264.056</v>
       </c>
       <c r="F33">
-        <v>212.102</v>
+        <v>218.944</v>
       </c>
       <c r="G33">
         <v>19</v>
@@ -3982,37 +3993,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M33">
-        <v>50.0136516</v>
+        <v>51.6269952</v>
       </c>
       <c r="N33">
-        <v>-54.74698493333334</v>
+        <v>-56.36032853333334</v>
       </c>
       <c r="O33">
-        <v>-15.32915578133334</v>
+        <v>-15.78089198933334</v>
       </c>
       <c r="P33">
-        <v>-39.417829152</v>
+        <v>-40.579436544</v>
       </c>
       <c r="Q33">
-        <v>53.982170848</v>
+        <v>52.820563456</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.106575175225166</v>
+        <v>0.1074689278020067</v>
       </c>
       <c r="T33">
-        <v>1.403583723444942</v>
+        <v>1.424224660554426</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.0264994314738925</v>
+        <v>-0.02567132424033335</v>
       </c>
       <c r="W33">
-        <v>0.2420485659415438</v>
+        <v>0.2418532982558706</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.0946408266924732</v>
+        <v>-0.09168330085833332</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4028,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1504719263472431</v>
+        <v>0.1523719263472431</v>
       </c>
       <c r="C34">
-        <v>137.7023695887708</v>
+        <v>126.6590115715906</v>
       </c>
       <c r="D34">
-        <v>337.6463695887708</v>
+        <v>333.4450115715906</v>
       </c>
       <c r="E34">
-        <v>-264.056</v>
+        <v>-257.2139999999999</v>
       </c>
       <c r="F34">
-        <v>218.944</v>
+        <v>225.786</v>
       </c>
       <c r="G34">
         <v>19</v>
@@ -4064,37 +4075,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M34">
-        <v>51.6269952</v>
+        <v>53.24033880000001</v>
       </c>
       <c r="N34">
-        <v>-56.36032853333334</v>
+        <v>-57.97367213333334</v>
       </c>
       <c r="O34">
-        <v>-15.78089198933334</v>
+        <v>-16.23262819733334</v>
       </c>
       <c r="P34">
-        <v>-40.579436544</v>
+        <v>-41.74104393600001</v>
       </c>
       <c r="Q34">
-        <v>52.820563456</v>
+        <v>51.65895606399999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1074689278020067</v>
+        <v>0.1083893595602456</v>
       </c>
       <c r="T34">
-        <v>1.424224660554426</v>
+        <v>1.445481745040313</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.02567132424033335</v>
+        <v>-0.02489340532395961</v>
       </c>
       <c r="W34">
-        <v>0.2418532982558706</v>
+        <v>0.2416698649753897</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.09168330085833332</v>
+        <v>-0.08890501901414138</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4110,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1523719263472431</v>
+        <v>0.1542719263472431</v>
       </c>
       <c r="C35">
-        <v>126.6590115715906</v>
+        <v>115.7189241498427</v>
       </c>
       <c r="D35">
-        <v>333.4450115715906</v>
+        <v>329.3469241498428</v>
       </c>
       <c r="E35">
-        <v>-257.2139999999999</v>
+        <v>-250.372</v>
       </c>
       <c r="F35">
-        <v>225.786</v>
+        <v>232.628</v>
       </c>
       <c r="G35">
         <v>19</v>
@@ -4146,37 +4157,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M35">
-        <v>53.24033880000001</v>
+        <v>54.85368240000001</v>
       </c>
       <c r="N35">
-        <v>-57.97367213333334</v>
+        <v>-59.58701573333335</v>
       </c>
       <c r="O35">
-        <v>-16.23262819733334</v>
+        <v>-16.68436440533334</v>
       </c>
       <c r="P35">
-        <v>-41.74104393600001</v>
+        <v>-42.902651328</v>
       </c>
       <c r="Q35">
-        <v>51.65895606399999</v>
+        <v>50.497348672</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1083893595602456</v>
+        <v>0.1093376831899463</v>
       </c>
       <c r="T35">
-        <v>1.445481745040313</v>
+        <v>1.46738298360153</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.02489340532395961</v>
+        <v>-0.02416124634384315</v>
       </c>
       <c r="W35">
-        <v>0.2416698649753897</v>
+        <v>0.2414972218878782</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.08890501901414138</v>
+        <v>-0.08629016551372559</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4192,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1542719263472431</v>
+        <v>0.1561719263472431</v>
       </c>
       <c r="C36">
-        <v>115.7189241498427</v>
+        <v>104.8783459200551</v>
       </c>
       <c r="D36">
-        <v>329.3469241498428</v>
+        <v>325.3483459200551</v>
       </c>
       <c r="E36">
-        <v>-250.372</v>
+        <v>-243.53</v>
       </c>
       <c r="F36">
-        <v>232.628</v>
+        <v>239.47</v>
       </c>
       <c r="G36">
         <v>19</v>
@@ -4228,37 +4239,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M36">
-        <v>54.85368240000001</v>
+        <v>56.46702600000001</v>
       </c>
       <c r="N36">
-        <v>-59.58701573333335</v>
+        <v>-61.20035933333335</v>
       </c>
       <c r="O36">
-        <v>-16.68436440533334</v>
+        <v>-17.13610061333334</v>
       </c>
       <c r="P36">
-        <v>-42.902651328</v>
+        <v>-44.06425872000001</v>
       </c>
       <c r="Q36">
-        <v>50.497348672</v>
+        <v>49.33574127999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1093376831899463</v>
+        <v>0.1103151860082531</v>
       </c>
       <c r="T36">
-        <v>1.46738298360153</v>
+        <v>1.489958106426169</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.02416124634384315</v>
+        <v>-0.02347092501973335</v>
       </c>
       <c r="W36">
-        <v>0.2414972218878782</v>
+        <v>0.2413344441196531</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.08629016551372559</v>
+        <v>-0.08382473221333342</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4274,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1561719263472431</v>
+        <v>0.1580719263472432</v>
       </c>
       <c r="C37">
-        <v>104.8783459200551</v>
+        <v>94.13369595535929</v>
       </c>
       <c r="D37">
-        <v>325.3483459200551</v>
+        <v>321.4456959553593</v>
       </c>
       <c r="E37">
-        <v>-243.53</v>
+        <v>-236.688</v>
       </c>
       <c r="F37">
-        <v>239.47</v>
+        <v>246.312</v>
       </c>
       <c r="G37">
         <v>19</v>
@@ -4310,37 +4321,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M37">
-        <v>56.46702600000001</v>
+        <v>58.08036960000001</v>
       </c>
       <c r="N37">
-        <v>-61.20035933333335</v>
+        <v>-62.81370293333335</v>
       </c>
       <c r="O37">
-        <v>-17.13610061333334</v>
+        <v>-17.58783682133334</v>
       </c>
       <c r="P37">
-        <v>-44.06425872000001</v>
+        <v>-45.22586611200001</v>
       </c>
       <c r="Q37">
-        <v>49.33574127999999</v>
+        <v>48.174133888</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1103151860082531</v>
+        <v>0.1113232357896321</v>
       </c>
       <c r="T37">
-        <v>1.489958106426169</v>
+        <v>1.513238701839078</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.02347092501973335</v>
+        <v>-0.02281895488029631</v>
       </c>
       <c r="W37">
-        <v>0.2413344441196531</v>
+        <v>0.2411807095607739</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.08382473221333342</v>
+        <v>-0.08149626742962957</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4356,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1580719263472431</v>
+        <v>0.1599719263472432</v>
       </c>
       <c r="C38">
-        <v>94.13369595535937</v>
+        <v>83.48156310944111</v>
       </c>
       <c r="D38">
-        <v>321.4456959553594</v>
+        <v>317.6355631094411</v>
       </c>
       <c r="E38">
-        <v>-236.688</v>
+        <v>-229.846</v>
       </c>
       <c r="F38">
-        <v>246.312</v>
+        <v>253.154</v>
       </c>
       <c r="G38">
         <v>19</v>
@@ -4392,37 +4403,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M38">
-        <v>58.0803696</v>
+        <v>59.6937132</v>
       </c>
       <c r="N38">
-        <v>-62.81370293333334</v>
+        <v>-64.42704653333334</v>
       </c>
       <c r="O38">
-        <v>-17.58783682133334</v>
+        <v>-18.03957302933334</v>
       </c>
       <c r="P38">
-        <v>-45.22586611200001</v>
+        <v>-46.387473504</v>
       </c>
       <c r="Q38">
-        <v>48.174133888</v>
+        <v>47.01252649600001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1113232357896321</v>
+        <v>0.1123632871513723</v>
       </c>
       <c r="T38">
-        <v>1.513238701839078</v>
+        <v>1.537258363773032</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.02281895488029631</v>
+        <v>-0.02220222637001803</v>
       </c>
       <c r="W38">
-        <v>0.2411807095607739</v>
+        <v>0.2410352849780503</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.08149626742962979</v>
+        <v>-0.07929366560720719</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4438,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1599719263472432</v>
+        <v>0.1618719263472431</v>
       </c>
       <c r="C39">
-        <v>83.48156310944111</v>
+        <v>72.91869607226829</v>
       </c>
       <c r="D39">
-        <v>317.6355631094411</v>
+        <v>313.9146960722683</v>
       </c>
       <c r="E39">
-        <v>-229.846</v>
+        <v>-223.004</v>
       </c>
       <c r="F39">
-        <v>253.154</v>
+        <v>259.996</v>
       </c>
       <c r="G39">
         <v>19</v>
@@ -4474,37 +4485,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M39">
-        <v>59.6937132</v>
+        <v>61.30705680000001</v>
       </c>
       <c r="N39">
-        <v>-64.42704653333334</v>
+        <v>-66.04039013333335</v>
       </c>
       <c r="O39">
-        <v>-18.03957302933334</v>
+        <v>-18.49130923733334</v>
       </c>
       <c r="P39">
-        <v>-46.387473504</v>
+        <v>-47.54908089600001</v>
       </c>
       <c r="Q39">
-        <v>47.01252649600001</v>
+        <v>45.850919104</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1123632871513723</v>
+        <v>0.1134368885570396</v>
       </c>
       <c r="T39">
-        <v>1.537258363773032</v>
+        <v>1.562052853511306</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.02220222637001803</v>
+        <v>-0.02161795725501756</v>
       </c>
       <c r="W39">
-        <v>0.2410352849780503</v>
+        <v>0.2408975143207331</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.07929366560720719</v>
+        <v>-0.07720699019649135</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4520,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1618719263472431</v>
+        <v>0.1637719263472431</v>
       </c>
       <c r="C40">
-        <v>72.91869607226829</v>
+        <v>62.44199411666546</v>
       </c>
       <c r="D40">
-        <v>313.9146960722683</v>
+        <v>310.2799941166655</v>
       </c>
       <c r="E40">
-        <v>-223.004</v>
+        <v>-216.162</v>
       </c>
       <c r="F40">
-        <v>259.996</v>
+        <v>266.838</v>
       </c>
       <c r="G40">
         <v>19</v>
@@ -4556,37 +4567,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M40">
-        <v>61.30705680000001</v>
+        <v>62.92040040000001</v>
       </c>
       <c r="N40">
-        <v>-66.04039013333335</v>
+        <v>-67.65373373333334</v>
       </c>
       <c r="O40">
-        <v>-18.49130923733334</v>
+        <v>-18.94304544533334</v>
       </c>
       <c r="P40">
-        <v>-47.54908089600001</v>
+        <v>-48.710688288</v>
       </c>
       <c r="Q40">
-        <v>45.850919104</v>
+        <v>44.68931171200001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1134368885570396</v>
+        <v>0.1145456900087943</v>
       </c>
       <c r="T40">
-        <v>1.562052853511306</v>
+        <v>1.587660277339361</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.02161795725501756</v>
+        <v>-0.02106365065873506</v>
       </c>
       <c r="W40">
-        <v>0.2408975143207331</v>
+        <v>0.2407668088253298</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.07720699019649135</v>
+        <v>-0.07522732378119668</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4602,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1637719263472431</v>
+        <v>0.1656719263472431</v>
       </c>
       <c r="C41">
-        <v>62.44199411666546</v>
+        <v>52.04849848038248</v>
       </c>
       <c r="D41">
-        <v>310.2799941166655</v>
+        <v>306.7284984803825</v>
       </c>
       <c r="E41">
-        <v>-216.162</v>
+        <v>-209.32</v>
       </c>
       <c r="F41">
-        <v>266.838</v>
+        <v>273.68</v>
       </c>
       <c r="G41">
         <v>19</v>
@@ -4638,37 +4649,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M41">
-        <v>62.92040040000001</v>
+        <v>64.533744</v>
       </c>
       <c r="N41">
-        <v>-67.65373373333334</v>
+        <v>-69.26707733333333</v>
       </c>
       <c r="O41">
-        <v>-18.94304544533334</v>
+        <v>-19.39478165333334</v>
       </c>
       <c r="P41">
-        <v>-48.710688288</v>
+        <v>-49.87229567999999</v>
       </c>
       <c r="Q41">
-        <v>44.68931171200001</v>
+        <v>43.52770432000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1145456900087943</v>
+        <v>0.1156914515089409</v>
       </c>
       <c r="T41">
-        <v>1.587660277339361</v>
+        <v>1.614121281961683</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.02106365065873506</v>
+        <v>-0.02053705939226668</v>
       </c>
       <c r="W41">
-        <v>0.2407668088253298</v>
+        <v>0.2406426386046965</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.07522732378119668</v>
+        <v>-0.07334664068666674</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4684,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1656719263472431</v>
+        <v>0.1675719263472431</v>
       </c>
       <c r="C42">
-        <v>52.04849848038248</v>
+        <v>41.73538433331498</v>
       </c>
       <c r="D42">
-        <v>306.7284984803825</v>
+        <v>303.257384333315</v>
       </c>
       <c r="E42">
-        <v>-209.32</v>
+        <v>-202.478</v>
       </c>
       <c r="F42">
-        <v>273.68</v>
+        <v>280.522</v>
       </c>
       <c r="G42">
         <v>19</v>
@@ -4720,37 +4731,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M42">
-        <v>64.533744</v>
+        <v>66.14708760000002</v>
       </c>
       <c r="N42">
-        <v>-69.26707733333333</v>
+        <v>-70.88042093333335</v>
       </c>
       <c r="O42">
-        <v>-19.39478165333334</v>
+        <v>-19.84651786133334</v>
       </c>
       <c r="P42">
-        <v>-49.87229567999999</v>
+        <v>-51.03390307200002</v>
       </c>
       <c r="Q42">
-        <v>43.52770432000001</v>
+        <v>42.36609692799999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1156914515089409</v>
+        <v>0.1168760523819738</v>
       </c>
       <c r="T42">
-        <v>1.614121281961683</v>
+        <v>1.641479269791542</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.02053705939226668</v>
+        <v>-0.02003615550465042</v>
       </c>
       <c r="W42">
-        <v>0.2406426386046965</v>
+        <v>0.2405245254679966</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.07334664068666674</v>
+        <v>-0.07155769823089431</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4766,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1675719263472431</v>
+        <v>0.1694719263472431</v>
       </c>
       <c r="C43">
-        <v>41.73538433331498</v>
+        <v>31.49995328404327</v>
       </c>
       <c r="D43">
-        <v>303.257384333315</v>
+        <v>299.8639532840433</v>
       </c>
       <c r="E43">
-        <v>-202.478</v>
+        <v>-195.636</v>
       </c>
       <c r="F43">
-        <v>280.522</v>
+        <v>287.364</v>
       </c>
       <c r="G43">
         <v>19</v>
@@ -4802,37 +4813,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M43">
-        <v>66.14708760000002</v>
+        <v>67.76043120000001</v>
       </c>
       <c r="N43">
-        <v>-70.88042093333335</v>
+        <v>-72.49376453333335</v>
       </c>
       <c r="O43">
-        <v>-19.84651786133334</v>
+        <v>-20.29825406933334</v>
       </c>
       <c r="P43">
-        <v>-51.03390307200002</v>
+        <v>-52.19551046400001</v>
       </c>
       <c r="Q43">
-        <v>42.36609692799999</v>
+        <v>41.204489536</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1168760523819738</v>
+        <v>0.1181015015609733</v>
       </c>
       <c r="T43">
-        <v>1.641479269791542</v>
+        <v>1.669780636512086</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.02003615550465042</v>
+        <v>-0.01955910418311112</v>
       </c>
       <c r="W43">
-        <v>0.2405245254679966</v>
+        <v>0.2404120367663776</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.07155769823089431</v>
+        <v>-0.06985394351111118</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4848,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1694719263472431</v>
+        <v>0.1713719263472431</v>
       </c>
       <c r="C44">
-        <v>31.49995328404333</v>
+        <v>21.33962638391137</v>
       </c>
       <c r="D44">
-        <v>299.8639532840434</v>
+        <v>296.5456263839114</v>
       </c>
       <c r="E44">
-        <v>-195.636</v>
+        <v>-188.794</v>
       </c>
       <c r="F44">
-        <v>287.364</v>
+        <v>294.206</v>
       </c>
       <c r="G44">
         <v>19</v>
@@ -4884,37 +4895,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M44">
-        <v>67.76043120000001</v>
+        <v>69.37377480000001</v>
       </c>
       <c r="N44">
-        <v>-72.49376453333335</v>
+        <v>-74.10710813333334</v>
       </c>
       <c r="O44">
-        <v>-20.29825406933334</v>
+        <v>-20.74999027733334</v>
       </c>
       <c r="P44">
-        <v>-52.19551046400001</v>
+        <v>-53.357117856</v>
       </c>
       <c r="Q44">
-        <v>41.204489536</v>
+        <v>40.042882144</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1181015015609733</v>
+        <v>0.1193699489567799</v>
       </c>
       <c r="T44">
-        <v>1.669780636512086</v>
+        <v>1.699075033643877</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.01955910418311112</v>
+        <v>-0.01910424129513179</v>
       </c>
       <c r="W44">
-        <v>0.2404120367663776</v>
+        <v>0.2403047800973921</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.06985394351111118</v>
+        <v>-0.06822943319689934</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4930,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1713719263472431</v>
+        <v>0.1732719263472431</v>
       </c>
       <c r="C45">
-        <v>21.33962638391137</v>
+        <v>11.25193759052797</v>
       </c>
       <c r="D45">
-        <v>296.5456263839114</v>
+        <v>293.299937590528</v>
       </c>
       <c r="E45">
-        <v>-188.794</v>
+        <v>-181.952</v>
       </c>
       <c r="F45">
-        <v>294.206</v>
+        <v>301.048</v>
       </c>
       <c r="G45">
         <v>19</v>
@@ -4966,37 +4977,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M45">
-        <v>69.37377480000001</v>
+        <v>70.9871184</v>
       </c>
       <c r="N45">
-        <v>-74.10710813333334</v>
+        <v>-75.72045173333333</v>
       </c>
       <c r="O45">
-        <v>-20.74999027733334</v>
+        <v>-21.20172648533334</v>
       </c>
       <c r="P45">
-        <v>-53.357117856</v>
+        <v>-54.518725248</v>
       </c>
       <c r="Q45">
-        <v>40.042882144</v>
+        <v>38.88127475200001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1193699489567799</v>
+        <v>0.1206836980452938</v>
       </c>
       <c r="T45">
-        <v>1.699075033643877</v>
+        <v>1.729415659244661</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.01910424129513179</v>
+        <v>-0.01867005399296971</v>
       </c>
       <c r="W45">
-        <v>0.2403047800973921</v>
+        <v>0.2402023987315423</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.06822943319689934</v>
+        <v>-0.06667876426060615</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5012,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1732719263472431</v>
+        <v>0.1751719263472431</v>
       </c>
       <c r="C46">
-        <v>11.25193759052797</v>
+        <v>1.234527655871716</v>
       </c>
       <c r="D46">
-        <v>293.299937590528</v>
+        <v>290.1245276558718</v>
       </c>
       <c r="E46">
-        <v>-181.952</v>
+        <v>-175.11</v>
       </c>
       <c r="F46">
-        <v>301.048</v>
+        <v>307.89</v>
       </c>
       <c r="G46">
         <v>19</v>
@@ -5048,37 +5059,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M46">
-        <v>70.9871184</v>
+        <v>72.60046200000001</v>
       </c>
       <c r="N46">
-        <v>-75.72045173333333</v>
+        <v>-77.33379533333334</v>
       </c>
       <c r="O46">
-        <v>-21.20172648533334</v>
+        <v>-21.65346269333334</v>
       </c>
       <c r="P46">
-        <v>-54.518725248</v>
+        <v>-55.68033264</v>
       </c>
       <c r="Q46">
-        <v>38.88127475200001</v>
+        <v>37.71966736</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1206836980452938</v>
+        <v>0.1220452198279355</v>
       </c>
       <c r="T46">
-        <v>1.729415659244661</v>
+        <v>1.760859580321836</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.01867005399296971</v>
+        <v>-0.01825516390423705</v>
       </c>
       <c r="W46">
-        <v>0.2402023987315423</v>
+        <v>0.2401045676486191</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.06667876426060615</v>
+        <v>-0.0651970139437037</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5094,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1751719263472431</v>
+        <v>0.1770719263472432</v>
       </c>
       <c r="C47">
-        <v>1.234527655871716</v>
+        <v>-8.714861592833472</v>
       </c>
       <c r="D47">
-        <v>290.1245276558718</v>
+        <v>287.0171384071666</v>
       </c>
       <c r="E47">
-        <v>-175.11</v>
+        <v>-168.268</v>
       </c>
       <c r="F47">
-        <v>307.89</v>
+        <v>314.732</v>
       </c>
       <c r="G47">
         <v>19</v>
@@ -5130,37 +5141,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M47">
-        <v>72.60046200000001</v>
+        <v>74.21380560000001</v>
       </c>
       <c r="N47">
-        <v>-77.33379533333334</v>
+        <v>-78.94713893333335</v>
       </c>
       <c r="O47">
-        <v>-21.65346269333334</v>
+        <v>-22.10519890133334</v>
       </c>
       <c r="P47">
-        <v>-55.68033264</v>
+        <v>-56.84194003200001</v>
       </c>
       <c r="Q47">
-        <v>37.71966736</v>
+        <v>36.55805996799999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1220452198279355</v>
+        <v>0.1234571683432677</v>
       </c>
       <c r="T47">
-        <v>1.760859580321836</v>
+        <v>1.793468091068537</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.01825516390423705</v>
+        <v>-0.0178583125150145</v>
       </c>
       <c r="W47">
-        <v>0.2401045676486191</v>
+        <v>0.2400109900910404</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.0651970139437037</v>
+        <v>-0.06377968755362318</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5176,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1770719263472432</v>
+        <v>0.1789719263472432</v>
       </c>
       <c r="C48">
-        <v>-8.714861592833472</v>
+        <v>-18.59839260860895</v>
       </c>
       <c r="D48">
-        <v>287.0171384071666</v>
+        <v>283.9756073913911</v>
       </c>
       <c r="E48">
-        <v>-168.268</v>
+        <v>-161.4259999999999</v>
       </c>
       <c r="F48">
-        <v>314.732</v>
+        <v>321.5740000000001</v>
       </c>
       <c r="G48">
         <v>19</v>
@@ -5212,37 +5223,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M48">
-        <v>74.21380560000001</v>
+        <v>75.82714920000002</v>
       </c>
       <c r="N48">
-        <v>-78.94713893333335</v>
+        <v>-80.56048253333336</v>
       </c>
       <c r="O48">
-        <v>-22.10519890133334</v>
+        <v>-22.55693510933334</v>
       </c>
       <c r="P48">
-        <v>-56.84194003200001</v>
+        <v>-58.00354742400002</v>
       </c>
       <c r="Q48">
-        <v>36.55805996799999</v>
+        <v>35.39645257599999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1234571683432677</v>
+        <v>0.1249223979346501</v>
       </c>
       <c r="T48">
-        <v>1.793468091068537</v>
+        <v>1.827307111654736</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.0178583125150145</v>
+        <v>-0.01747834841895037</v>
       </c>
       <c r="W48">
-        <v>0.2400109900910404</v>
+        <v>0.2399213945571885</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.06377968755362318</v>
+        <v>-0.06242267292482273</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5258,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1789719263472432</v>
+        <v>0.1808719263472431</v>
       </c>
       <c r="C49">
-        <v>-18.59839260860895</v>
+        <v>-28.41813714326781</v>
       </c>
       <c r="D49">
-        <v>283.9756073913911</v>
+        <v>280.9978628567322</v>
       </c>
       <c r="E49">
-        <v>-161.4259999999999</v>
+        <v>-154.5839999999999</v>
       </c>
       <c r="F49">
-        <v>321.5740000000001</v>
+        <v>328.4160000000001</v>
       </c>
       <c r="G49">
         <v>19</v>
@@ -5294,37 +5305,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M49">
-        <v>75.82714920000002</v>
+        <v>77.44049280000002</v>
       </c>
       <c r="N49">
-        <v>-80.56048253333336</v>
+        <v>-82.17382613333335</v>
       </c>
       <c r="O49">
-        <v>-22.55693510933334</v>
+        <v>-23.00867131733334</v>
       </c>
       <c r="P49">
-        <v>-58.00354742400002</v>
+        <v>-59.16515481600001</v>
       </c>
       <c r="Q49">
-        <v>35.39645257599999</v>
+        <v>34.23484518399999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1249223979346501</v>
+        <v>0.1264439825103164</v>
       </c>
       <c r="T49">
-        <v>1.827307111654736</v>
+        <v>1.862447633032712</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.01747834841895037</v>
+        <v>-0.01711421616022223</v>
       </c>
       <c r="W49">
-        <v>0.2399213945571885</v>
+        <v>0.2398355321705804</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.06242267292482273</v>
+        <v>-0.06112220057222228</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5340,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1808719263472431</v>
+        <v>0.1827719263472432</v>
       </c>
       <c r="C50">
-        <v>-28.41813714326776</v>
+        <v>-38.17608095349408</v>
       </c>
       <c r="D50">
-        <v>280.9978628567322</v>
+        <v>278.081919046506</v>
       </c>
       <c r="E50">
-        <v>-154.584</v>
+        <v>-147.742</v>
       </c>
       <c r="F50">
-        <v>328.416</v>
+        <v>335.258</v>
       </c>
       <c r="G50">
         <v>19</v>
@@ -5376,37 +5387,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M50">
-        <v>77.4404928</v>
+        <v>79.05383640000001</v>
       </c>
       <c r="N50">
-        <v>-82.17382613333334</v>
+        <v>-83.78716973333334</v>
       </c>
       <c r="O50">
-        <v>-23.00867131733333</v>
+        <v>-23.46040752533334</v>
       </c>
       <c r="P50">
-        <v>-59.165154816</v>
+        <v>-60.32676220800001</v>
       </c>
       <c r="Q50">
-        <v>34.23484518400001</v>
+        <v>33.073237792</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1264439825103164</v>
+        <v>0.1280252370693422</v>
       </c>
       <c r="T50">
-        <v>1.862447633032711</v>
+        <v>1.898966214072568</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.01711421616022224</v>
+        <v>-0.01676494644266668</v>
       </c>
       <c r="W50">
-        <v>0.2398355321705804</v>
+        <v>0.2397531743711808</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.06112220057222228</v>
+        <v>-0.05987480872380946</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5422,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1827719263472432</v>
+        <v>0.1846719263472431</v>
       </c>
       <c r="C51">
-        <v>-38.17608095349408</v>
+        <v>-47.87412821691828</v>
       </c>
       <c r="D51">
-        <v>278.081919046506</v>
+        <v>275.2258717830817</v>
       </c>
       <c r="E51">
-        <v>-147.742</v>
+        <v>-140.9</v>
       </c>
       <c r="F51">
-        <v>335.258</v>
+        <v>342.1</v>
       </c>
       <c r="G51">
         <v>19</v>
@@ -5458,37 +5469,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M51">
-        <v>79.05383640000001</v>
+        <v>80.66718</v>
       </c>
       <c r="N51">
-        <v>-83.78716973333334</v>
+        <v>-85.40051333333334</v>
       </c>
       <c r="O51">
-        <v>-23.46040752533334</v>
+        <v>-23.91214373333334</v>
       </c>
       <c r="P51">
-        <v>-60.32676220800001</v>
+        <v>-61.4883696</v>
       </c>
       <c r="Q51">
-        <v>33.073237792</v>
+        <v>31.91163040000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1280252370693422</v>
+        <v>0.1296697418107291</v>
       </c>
       <c r="T51">
-        <v>1.898966214072568</v>
+        <v>1.93694553835402</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.01676494644266668</v>
+        <v>-0.01642964751381334</v>
       </c>
       <c r="W51">
-        <v>0.2397531743711808</v>
+        <v>0.2396741108837572</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.05987480872380946</v>
+        <v>-0.05867731254933339</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5504,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1846719263472431</v>
+        <v>0.1865719263472431</v>
       </c>
       <c r="C52">
-        <v>-47.87412821691828</v>
+        <v>-57.51410567882681</v>
       </c>
       <c r="D52">
-        <v>275.2258717830817</v>
+        <v>272.4278943211732</v>
       </c>
       <c r="E52">
-        <v>-140.9</v>
+        <v>-134.058</v>
       </c>
       <c r="F52">
-        <v>342.1</v>
+        <v>348.942</v>
       </c>
       <c r="G52">
         <v>19</v>
@@ -5540,37 +5551,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M52">
-        <v>80.66718</v>
+        <v>82.28052360000001</v>
       </c>
       <c r="N52">
-        <v>-85.40051333333334</v>
+        <v>-87.01385693333334</v>
       </c>
       <c r="O52">
-        <v>-23.91214373333334</v>
+        <v>-24.36387994133334</v>
       </c>
       <c r="P52">
-        <v>-61.4883696</v>
+        <v>-62.64997699200001</v>
       </c>
       <c r="Q52">
-        <v>31.91163040000001</v>
+        <v>30.750023008</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1296697418107291</v>
+        <v>0.1313813691946215</v>
       </c>
       <c r="T52">
-        <v>1.93694553835402</v>
+        <v>1.976475039136755</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.01642964751381334</v>
+        <v>-0.0161074975625621</v>
       </c>
       <c r="W52">
-        <v>0.2396741108837572</v>
+        <v>0.2395981479252522</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.05867731254933339</v>
+        <v>-0.05752677700915032</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5586,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1865719263472431</v>
+        <v>0.1884719263472431</v>
       </c>
       <c r="C53">
-        <v>-57.51410567882681</v>
+        <v>-67.09776654848184</v>
       </c>
       <c r="D53">
-        <v>272.4278943211732</v>
+        <v>269.6862334515182</v>
       </c>
       <c r="E53">
-        <v>-134.058</v>
+        <v>-127.216</v>
       </c>
       <c r="F53">
-        <v>348.942</v>
+        <v>355.784</v>
       </c>
       <c r="G53">
         <v>19</v>
@@ -5622,37 +5633,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M53">
-        <v>82.28052360000001</v>
+        <v>83.89386720000002</v>
       </c>
       <c r="N53">
-        <v>-87.01385693333334</v>
+        <v>-88.62720053333335</v>
       </c>
       <c r="O53">
-        <v>-24.36387994133334</v>
+        <v>-24.81561614933334</v>
       </c>
       <c r="P53">
-        <v>-62.64997699200001</v>
+        <v>-63.81158438400001</v>
       </c>
       <c r="Q53">
-        <v>30.750023008</v>
+        <v>29.58841561599999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1313813691946215</v>
+        <v>0.1331643143861761</v>
       </c>
       <c r="T53">
-        <v>1.976475039136755</v>
+        <v>2.017651602452104</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.0161074975625621</v>
+        <v>-0.01579773799405129</v>
       </c>
       <c r="W53">
-        <v>0.2395981479252522</v>
+        <v>0.2395251066189973</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.05752677700915032</v>
+        <v>-0.05642049283589756</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5668,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1884719263472431</v>
+        <v>0.1903719263472431</v>
       </c>
       <c r="C54">
-        <v>-67.09776654848184</v>
+        <v>-76.62679416251393</v>
       </c>
       <c r="D54">
-        <v>269.6862334515182</v>
+        <v>266.9992058374861</v>
       </c>
       <c r="E54">
-        <v>-127.216</v>
+        <v>-120.374</v>
       </c>
       <c r="F54">
-        <v>355.784</v>
+        <v>362.626</v>
       </c>
       <c r="G54">
         <v>19</v>
@@ -5704,37 +5715,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M54">
-        <v>83.89386720000002</v>
+        <v>85.50721080000001</v>
       </c>
       <c r="N54">
-        <v>-88.62720053333335</v>
+        <v>-90.24054413333334</v>
       </c>
       <c r="O54">
-        <v>-24.81561614933334</v>
+        <v>-25.26735235733334</v>
       </c>
       <c r="P54">
-        <v>-63.81158438400001</v>
+        <v>-64.97319177600001</v>
       </c>
       <c r="Q54">
-        <v>29.58841561599999</v>
+        <v>28.426808224</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1331643143861761</v>
+        <v>0.135023129585882</v>
       </c>
       <c r="T54">
-        <v>2.017651602452104</v>
+        <v>2.060580359951085</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.01579773799405129</v>
+        <v>-0.01549966746586165</v>
       </c>
       <c r="W54">
-        <v>0.2395251066189973</v>
+        <v>0.2394548215884502</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.05642049283589756</v>
+        <v>-0.05535595523522008</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5750,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1903719263472431</v>
+        <v>0.1922719263472431</v>
       </c>
       <c r="C55">
-        <v>-76.62679416251393</v>
+        <v>-86.10280543147354</v>
       </c>
       <c r="D55">
-        <v>266.9992058374861</v>
+        <v>264.3651945685265</v>
       </c>
       <c r="E55">
-        <v>-120.374</v>
+        <v>-113.5319999999999</v>
       </c>
       <c r="F55">
-        <v>362.626</v>
+        <v>369.4680000000001</v>
       </c>
       <c r="G55">
         <v>19</v>
@@ -5786,37 +5797,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M55">
-        <v>85.50721080000001</v>
+        <v>87.12055440000002</v>
       </c>
       <c r="N55">
-        <v>-90.24054413333334</v>
+        <v>-91.85388773333335</v>
       </c>
       <c r="O55">
-        <v>-25.26735235733334</v>
+        <v>-25.71908856533334</v>
       </c>
       <c r="P55">
-        <v>-64.97319177600001</v>
+        <v>-66.13479916800001</v>
       </c>
       <c r="Q55">
-        <v>28.426808224</v>
+        <v>27.26520083199999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.135023129585882</v>
+        <v>0.136962762837749</v>
       </c>
       <c r="T55">
-        <v>2.060580359951085</v>
+        <v>2.105375585167413</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.01549966746586165</v>
+        <v>-0.01521263658686421</v>
       </c>
       <c r="W55">
-        <v>0.2394548215884502</v>
+        <v>0.2393871397071826</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.05535595523522008</v>
+        <v>-0.05433084495308638</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5832,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1922719263472431</v>
+        <v>0.1941719263472431</v>
       </c>
       <c r="C56">
-        <v>-86.10280543147354</v>
+        <v>-95.52735408436928</v>
       </c>
       <c r="D56">
-        <v>264.3651945685265</v>
+        <v>261.7826459156308</v>
       </c>
       <c r="E56">
-        <v>-113.5319999999999</v>
+        <v>-106.6899999999999</v>
       </c>
       <c r="F56">
-        <v>369.4680000000001</v>
+        <v>376.3100000000001</v>
       </c>
       <c r="G56">
         <v>19</v>
@@ -5868,37 +5879,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M56">
-        <v>87.12055440000002</v>
+        <v>88.73389800000001</v>
       </c>
       <c r="N56">
-        <v>-91.85388773333335</v>
+        <v>-93.46723133333334</v>
       </c>
       <c r="O56">
-        <v>-25.71908856533334</v>
+        <v>-26.17082477333334</v>
       </c>
       <c r="P56">
-        <v>-66.13479916800001</v>
+        <v>-67.29640656000001</v>
       </c>
       <c r="Q56">
-        <v>27.26520083199999</v>
+        <v>26.10359344</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.136962762837749</v>
+        <v>0.1389886020119212</v>
       </c>
       <c r="T56">
-        <v>2.105375585167413</v>
+        <v>2.152161709282244</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.01521263658686421</v>
+        <v>-0.01493604319437577</v>
       </c>
       <c r="W56">
-        <v>0.2393871397071826</v>
+        <v>0.2393219189852338</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.05433084495308638</v>
+        <v>-0.05334301140848496</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5914,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1941719263472431</v>
+        <v>0.1960719263472431</v>
       </c>
       <c r="C57">
-        <v>-95.52735408436928</v>
+        <v>-104.9019337248728</v>
       </c>
       <c r="D57">
-        <v>261.7826459156308</v>
+        <v>259.2500662751273</v>
       </c>
       <c r="E57">
-        <v>-106.6899999999999</v>
+        <v>-99.84799999999996</v>
       </c>
       <c r="F57">
-        <v>376.3100000000001</v>
+        <v>383.152</v>
       </c>
       <c r="G57">
         <v>19</v>
@@ -5950,37 +5961,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M57">
-        <v>88.73389800000001</v>
+        <v>90.34724160000002</v>
       </c>
       <c r="N57">
-        <v>-93.46723133333334</v>
+        <v>-95.08057493333335</v>
       </c>
       <c r="O57">
-        <v>-26.17082477333334</v>
+        <v>-26.62256098133334</v>
       </c>
       <c r="P57">
-        <v>-67.29640656000001</v>
+        <v>-68.45801395200002</v>
       </c>
       <c r="Q57">
-        <v>26.10359344</v>
+        <v>24.94198604799999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1389886020119212</v>
+        <v>0.1411065247849194</v>
       </c>
       <c r="T57">
-        <v>2.152161709282244</v>
+        <v>2.201074475402296</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.01493604319437577</v>
+        <v>-0.01466932813733334</v>
       </c>
       <c r="W57">
-        <v>0.2393219189852338</v>
+        <v>0.2392590275747832</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.05334301140848496</v>
+        <v>-0.05239045763333339</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5996,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1960719263472431</v>
+        <v>0.1979719263472431</v>
       </c>
       <c r="C58">
-        <v>-104.9019337248728</v>
+        <v>-114.2279807118221</v>
       </c>
       <c r="D58">
-        <v>259.2500662751273</v>
+        <v>256.766019288178</v>
       </c>
       <c r="E58">
-        <v>-99.84799999999996</v>
+        <v>-93.00599999999991</v>
       </c>
       <c r="F58">
-        <v>383.152</v>
+        <v>389.9940000000001</v>
       </c>
       <c r="G58">
         <v>19</v>
@@ -6032,37 +6043,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M58">
-        <v>90.34724160000002</v>
+        <v>91.96058520000003</v>
       </c>
       <c r="N58">
-        <v>-95.08057493333335</v>
+        <v>-96.69391853333336</v>
       </c>
       <c r="O58">
-        <v>-26.62256098133334</v>
+        <v>-27.07429718933334</v>
       </c>
       <c r="P58">
-        <v>-68.45801395200002</v>
+        <v>-69.61962134400002</v>
       </c>
       <c r="Q58">
-        <v>24.94198604799999</v>
+        <v>23.78037865599998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1411065247849194</v>
+        <v>0.143322955593871</v>
       </c>
       <c r="T58">
-        <v>2.201074475402296</v>
+        <v>2.252262253900024</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.01466932813733334</v>
+        <v>-0.01441197150334504</v>
       </c>
       <c r="W58">
-        <v>0.2392590275747832</v>
+        <v>0.2391983428804888</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.05239045763333339</v>
+        <v>-0.05147132679766075</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6078,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1979719263472431</v>
+        <v>0.1998719263472432</v>
       </c>
       <c r="C59">
-        <v>-114.2279807118221</v>
+        <v>-123.5068768756979</v>
       </c>
       <c r="D59">
-        <v>256.766019288178</v>
+        <v>254.3291231243022</v>
       </c>
       <c r="E59">
-        <v>-93.00599999999991</v>
+        <v>-86.16399999999993</v>
       </c>
       <c r="F59">
-        <v>389.9940000000001</v>
+        <v>396.8360000000001</v>
       </c>
       <c r="G59">
         <v>19</v>
@@ -6114,37 +6125,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M59">
-        <v>91.96058520000003</v>
+        <v>93.57392880000002</v>
       </c>
       <c r="N59">
-        <v>-96.69391853333336</v>
+        <v>-98.30726213333335</v>
       </c>
       <c r="O59">
-        <v>-27.07429718933334</v>
+        <v>-27.52603339733334</v>
       </c>
       <c r="P59">
-        <v>-69.61962134400002</v>
+        <v>-70.781228736</v>
       </c>
       <c r="Q59">
-        <v>23.78037865599998</v>
+        <v>22.618771264</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.143322955593871</v>
+        <v>0.1456449307270584</v>
       </c>
       <c r="T59">
-        <v>2.252262253900024</v>
+        <v>2.305887545659548</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.01441197150334504</v>
+        <v>-0.01416348923604599</v>
       </c>
       <c r="W59">
-        <v>0.2391983428804888</v>
+        <v>0.2391397507618597</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.05147132679766075</v>
+        <v>-0.05058389012873565</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6160,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1998719263472431</v>
+        <v>0.2017719263472431</v>
       </c>
       <c r="C60">
-        <v>-123.5068768756978</v>
+        <v>-132.7399520818643</v>
       </c>
       <c r="D60">
-        <v>254.3291231243022</v>
+        <v>251.9380479181357</v>
       </c>
       <c r="E60">
-        <v>-86.16399999999999</v>
+        <v>-79.322</v>
       </c>
       <c r="F60">
-        <v>396.836</v>
+        <v>403.678</v>
       </c>
       <c r="G60">
         <v>19</v>
@@ -6196,37 +6207,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M60">
-        <v>93.5739288</v>
+        <v>95.1872724</v>
       </c>
       <c r="N60">
-        <v>-98.30726213333334</v>
+        <v>-99.92060573333333</v>
       </c>
       <c r="O60">
-        <v>-27.52603339733334</v>
+        <v>-27.97776960533334</v>
       </c>
       <c r="P60">
-        <v>-70.781228736</v>
+        <v>-71.942836128</v>
       </c>
       <c r="Q60">
-        <v>22.618771264</v>
+        <v>21.45716387200001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1456449307270584</v>
+        <v>0.1480801729399135</v>
       </c>
       <c r="T60">
-        <v>2.305887545659547</v>
+        <v>2.36212870530978</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.01416348923604599</v>
+        <v>-0.01392343009645199</v>
       </c>
       <c r="W60">
-        <v>0.2391397507618597</v>
+        <v>0.2390831448167434</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.05058389012873565</v>
+        <v>-0.0497265360587571</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6242,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2017719263472431</v>
+        <v>0.2036719263472431</v>
       </c>
       <c r="C61">
-        <v>-132.7399520818643</v>
+        <v>-141.9284866505686</v>
       </c>
       <c r="D61">
-        <v>251.9380479181357</v>
+        <v>249.5915133494314</v>
       </c>
       <c r="E61">
-        <v>-79.322</v>
+        <v>-72.47999999999996</v>
       </c>
       <c r="F61">
-        <v>403.678</v>
+        <v>410.52</v>
       </c>
       <c r="G61">
         <v>19</v>
@@ -6278,37 +6289,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M61">
-        <v>95.1872724</v>
+        <v>96.80061600000002</v>
       </c>
       <c r="N61">
-        <v>-99.92060573333333</v>
+        <v>-101.5339493333334</v>
       </c>
       <c r="O61">
-        <v>-27.97776960533334</v>
+        <v>-28.42950581333334</v>
       </c>
       <c r="P61">
-        <v>-71.942836128</v>
+        <v>-73.10444352000002</v>
       </c>
       <c r="Q61">
-        <v>21.45716387200001</v>
+        <v>20.29555647999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1480801729399135</v>
+        <v>0.1506371772634113</v>
       </c>
       <c r="T61">
-        <v>2.36212870530978</v>
+        <v>2.421181922942524</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.01392343009645199</v>
+        <v>-0.01369137292817778</v>
       </c>
       <c r="W61">
-        <v>0.2390831448167434</v>
+        <v>0.2390284257364643</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.0497265360587571</v>
+        <v>-0.04889776045777783</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6324,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2036719263472431</v>
+        <v>0.2055719263472431</v>
       </c>
       <c r="C62">
-        <v>-141.9284866505686</v>
+        <v>-151.0737136429481</v>
       </c>
       <c r="D62">
-        <v>249.5915133494314</v>
+        <v>247.2882863570519</v>
       </c>
       <c r="E62">
-        <v>-72.47999999999996</v>
+        <v>-65.63799999999998</v>
       </c>
       <c r="F62">
-        <v>410.52</v>
+        <v>417.362</v>
       </c>
       <c r="G62">
         <v>19</v>
@@ -6360,37 +6371,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M62">
-        <v>96.80061600000002</v>
+        <v>98.41395960000001</v>
       </c>
       <c r="N62">
-        <v>-101.5339493333334</v>
+        <v>-103.1472929333333</v>
       </c>
       <c r="O62">
-        <v>-28.42950581333334</v>
+        <v>-28.88124202133334</v>
       </c>
       <c r="P62">
-        <v>-73.10444352000002</v>
+        <v>-74.26605091200001</v>
       </c>
       <c r="Q62">
-        <v>20.29555647999999</v>
+        <v>19.13394908799999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1506371772634113</v>
+        <v>0.1533253100137552</v>
       </c>
       <c r="T62">
-        <v>2.421181922942524</v>
+        <v>2.483263510710283</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.01369137292817778</v>
+        <v>-0.01346692419165028</v>
       </c>
       <c r="W62">
-        <v>0.2390284257364643</v>
+        <v>0.2389755007243911</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.04889776045777783</v>
+        <v>-0.04809615782732246</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6406,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2055719263472431</v>
+        <v>0.2074719263472431</v>
       </c>
       <c r="C63">
-        <v>-151.0737136429481</v>
+        <v>-160.1768210216252</v>
       </c>
       <c r="D63">
-        <v>247.2882863570519</v>
+        <v>245.0271789783747</v>
       </c>
       <c r="E63">
-        <v>-65.63799999999998</v>
+        <v>-58.79599999999999</v>
       </c>
       <c r="F63">
-        <v>417.362</v>
+        <v>424.204</v>
       </c>
       <c r="G63">
         <v>19</v>
@@ -6442,37 +6453,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M63">
-        <v>98.41395960000001</v>
+        <v>100.0273032</v>
       </c>
       <c r="N63">
-        <v>-103.1472929333333</v>
+        <v>-104.7606365333333</v>
       </c>
       <c r="O63">
-        <v>-28.88124202133334</v>
+        <v>-29.33297822933334</v>
       </c>
       <c r="P63">
-        <v>-74.26605091200001</v>
+        <v>-75.427658304</v>
       </c>
       <c r="Q63">
-        <v>19.13394908799999</v>
+        <v>17.972341696</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1533253100137552</v>
+        <v>0.1561549234351698</v>
       </c>
       <c r="T63">
-        <v>2.483263510710283</v>
+        <v>2.548612550465816</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.01346692419165028</v>
+        <v>-0.01324971573694625</v>
       </c>
       <c r="W63">
-        <v>0.2389755007243911</v>
+        <v>0.2389242829707719</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.04809615782732246</v>
+        <v>-0.0473204133462366</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6488,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2074719263472431</v>
+        <v>0.2093719263472431</v>
       </c>
       <c r="C64">
-        <v>-160.1768210216252</v>
+        <v>-169.2389536938416</v>
       </c>
       <c r="D64">
-        <v>245.0271789783747</v>
+        <v>242.8070463061584</v>
       </c>
       <c r="E64">
-        <v>-58.79599999999999</v>
+        <v>-51.95399999999995</v>
       </c>
       <c r="F64">
-        <v>424.204</v>
+        <v>431.046</v>
       </c>
       <c r="G64">
         <v>19</v>
@@ -6524,37 +6535,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M64">
-        <v>100.0273032</v>
+        <v>101.6406468</v>
       </c>
       <c r="N64">
-        <v>-104.7606365333333</v>
+        <v>-106.3739801333333</v>
       </c>
       <c r="O64">
-        <v>-29.33297822933334</v>
+        <v>-29.78471443733334</v>
       </c>
       <c r="P64">
-        <v>-75.427658304</v>
+        <v>-76.58926569600001</v>
       </c>
       <c r="Q64">
-        <v>17.972341696</v>
+        <v>16.81073430399999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1561549234351698</v>
+        <v>0.1591374889334176</v>
       </c>
       <c r="T64">
-        <v>2.548612550465816</v>
+        <v>2.617493970748675</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.01324971573694625</v>
+        <v>-0.01303940278874075</v>
       </c>
       <c r="W64">
-        <v>0.2389242829707719</v>
+        <v>0.2388746911775851</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.0473204133462366</v>
+        <v>-0.0465692956740742</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6570,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2093719263472431</v>
+        <v>0.2112719263472431</v>
       </c>
       <c r="C65">
-        <v>-169.2389536938416</v>
+        <v>-178.2612154445151</v>
       </c>
       <c r="D65">
-        <v>242.8070463061584</v>
+        <v>240.626784555485</v>
       </c>
       <c r="E65">
-        <v>-51.95399999999995</v>
+        <v>-45.11199999999997</v>
       </c>
       <c r="F65">
-        <v>431.046</v>
+        <v>437.888</v>
       </c>
       <c r="G65">
         <v>19</v>
@@ -6606,37 +6617,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M65">
-        <v>101.6406468</v>
+        <v>103.2539904</v>
       </c>
       <c r="N65">
-        <v>-106.3739801333333</v>
+        <v>-107.9873237333333</v>
       </c>
       <c r="O65">
-        <v>-29.78471443733334</v>
+        <v>-30.23645064533334</v>
       </c>
       <c r="P65">
-        <v>-76.58926569600001</v>
+        <v>-77.75087308800001</v>
       </c>
       <c r="Q65">
-        <v>16.81073430399999</v>
+        <v>15.649126912</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1591374889334176</v>
+        <v>0.1622857525149015</v>
       </c>
       <c r="T65">
-        <v>2.617493970748675</v>
+        <v>2.690202136602806</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.01303940278874075</v>
+        <v>-0.01283566212016668</v>
       </c>
       <c r="W65">
-        <v>0.2388746911775851</v>
+        <v>0.2388266491279353</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.0465692956740742</v>
+        <v>-0.04584165042916677</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6652,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2112719263472431</v>
+        <v>0.2131719263472431</v>
       </c>
       <c r="C66">
-        <v>-178.2612154445151</v>
+        <v>-187.2446707660789</v>
       </c>
       <c r="D66">
-        <v>240.626784555485</v>
+        <v>238.4853292339211</v>
       </c>
       <c r="E66">
-        <v>-45.11199999999997</v>
+        <v>-38.26999999999998</v>
       </c>
       <c r="F66">
-        <v>437.888</v>
+        <v>444.73</v>
       </c>
       <c r="G66">
         <v>19</v>
@@ -6688,37 +6699,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M66">
-        <v>103.2539904</v>
+        <v>104.867334</v>
       </c>
       <c r="N66">
-        <v>-107.9873237333333</v>
+        <v>-109.6006673333333</v>
       </c>
       <c r="O66">
-        <v>-30.23645064533334</v>
+        <v>-30.68818685333334</v>
       </c>
       <c r="P66">
-        <v>-77.75087308800001</v>
+        <v>-78.91248048</v>
       </c>
       <c r="Q66">
-        <v>15.649126912</v>
+        <v>14.48751952000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1622857525149015</v>
+        <v>0.1656139168724701</v>
       </c>
       <c r="T66">
-        <v>2.690202136602806</v>
+        <v>2.767065054791458</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.01283566212016668</v>
+        <v>-0.01263819039524103</v>
       </c>
       <c r="W66">
-        <v>0.2388266491279353</v>
+        <v>0.2387800852951978</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.04584165042916677</v>
+        <v>-0.04513639426871796</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6734,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2131719263472431</v>
+        <v>0.2150719263472431</v>
       </c>
       <c r="C67">
-        <v>-187.2446707660789</v>
+        <v>-196.1903465914731</v>
       </c>
       <c r="D67">
-        <v>238.4853292339211</v>
+        <v>236.3816534085269</v>
       </c>
       <c r="E67">
-        <v>-38.26999999999998</v>
+        <v>-31.42799999999994</v>
       </c>
       <c r="F67">
-        <v>444.73</v>
+        <v>451.5720000000001</v>
       </c>
       <c r="G67">
         <v>19</v>
@@ -6770,37 +6781,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M67">
-        <v>104.867334</v>
+        <v>106.4806776</v>
       </c>
       <c r="N67">
-        <v>-109.6006673333333</v>
+        <v>-111.2140109333334</v>
       </c>
       <c r="O67">
-        <v>-30.68818685333334</v>
+        <v>-31.13992306133334</v>
       </c>
       <c r="P67">
-        <v>-78.91248048</v>
+        <v>-80.07408787200001</v>
       </c>
       <c r="Q67">
-        <v>14.48751952000001</v>
+        <v>13.325912128</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1656139168724701</v>
+        <v>0.1691378556040133</v>
       </c>
       <c r="T67">
-        <v>2.767065054791458</v>
+        <v>2.848449321108853</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.01263819039524103</v>
+        <v>-0.0124467026619798</v>
       </c>
       <c r="W67">
-        <v>0.2387800852951978</v>
+        <v>0.2387349324876949</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.04513639426871796</v>
+        <v>-0.04445250950707069</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6816,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2150719263472431</v>
+        <v>0.2169719263472432</v>
       </c>
       <c r="C68">
-        <v>-196.1903465914731</v>
+        <v>-205.0992339362196</v>
       </c>
       <c r="D68">
-        <v>236.3816534085269</v>
+        <v>234.3147660637804</v>
       </c>
       <c r="E68">
-        <v>-31.42799999999994</v>
+        <v>-24.58599999999996</v>
       </c>
       <c r="F68">
-        <v>451.5720000000001</v>
+        <v>458.414</v>
       </c>
       <c r="G68">
         <v>19</v>
@@ -6852,37 +6863,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M68">
-        <v>106.4806776</v>
+        <v>108.0940212</v>
       </c>
       <c r="N68">
-        <v>-111.2140109333334</v>
+        <v>-112.8273545333333</v>
       </c>
       <c r="O68">
-        <v>-31.13992306133334</v>
+        <v>-31.59165926933334</v>
       </c>
       <c r="P68">
-        <v>-80.07408787200001</v>
+        <v>-81.23569526400001</v>
       </c>
       <c r="Q68">
-        <v>13.325912128</v>
+        <v>12.16430473599999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1691378556040133</v>
+        <v>0.1728753663798926</v>
       </c>
       <c r="T68">
-        <v>2.848449321108853</v>
+        <v>2.934765967203061</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.0124467026619798</v>
+        <v>-0.01226093098045772</v>
       </c>
       <c r="W68">
-        <v>0.2387349324876949</v>
+        <v>0.2386911275251919</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.04445250950707069</v>
+        <v>-0.04378903921592037</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6898,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2169719263472432</v>
+        <v>0.2188719263472431</v>
       </c>
       <c r="C69">
-        <v>-205.0992339362196</v>
+        <v>-213.9722894550939</v>
       </c>
       <c r="D69">
-        <v>234.3147660637804</v>
+        <v>232.2837105449062</v>
       </c>
       <c r="E69">
-        <v>-24.58599999999996</v>
+        <v>-17.74399999999991</v>
       </c>
       <c r="F69">
-        <v>458.414</v>
+        <v>465.2560000000001</v>
       </c>
       <c r="G69">
         <v>19</v>
@@ -6934,37 +6945,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M69">
-        <v>108.0940212</v>
+        <v>109.7073648</v>
       </c>
       <c r="N69">
-        <v>-112.8273545333333</v>
+        <v>-114.4406981333334</v>
       </c>
       <c r="O69">
-        <v>-31.59165926933334</v>
+        <v>-32.04339547733334</v>
       </c>
       <c r="P69">
-        <v>-81.23569526400001</v>
+        <v>-82.39730265600002</v>
       </c>
       <c r="Q69">
-        <v>12.16430473599999</v>
+        <v>11.00269734399998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1728753663798926</v>
+        <v>0.1768464715792642</v>
       </c>
       <c r="T69">
-        <v>2.934765967203061</v>
+        <v>3.026477403678157</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.01226093098045772</v>
+        <v>-0.01208062317192158</v>
       </c>
       <c r="W69">
-        <v>0.2386911275251919</v>
+        <v>0.2386486109439391</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.04378903921592037</v>
+        <v>-0.04314508275686268</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6980,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2188719263472431</v>
+        <v>0.2207719263472431</v>
       </c>
       <c r="C70">
-        <v>-213.9722894550939</v>
+        <v>-222.8104369185338</v>
       </c>
       <c r="D70">
-        <v>232.2837105449062</v>
+        <v>230.2875630814663</v>
       </c>
       <c r="E70">
-        <v>-17.74399999999991</v>
+        <v>-10.90199999999993</v>
       </c>
       <c r="F70">
-        <v>465.2560000000001</v>
+        <v>472.0980000000001</v>
       </c>
       <c r="G70">
         <v>19</v>
@@ -7016,37 +7027,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M70">
-        <v>109.7073648</v>
+        <v>111.3207084</v>
       </c>
       <c r="N70">
-        <v>-114.4406981333334</v>
+        <v>-116.0540417333333</v>
       </c>
       <c r="O70">
-        <v>-32.04339547733334</v>
+        <v>-32.49513168533334</v>
       </c>
       <c r="P70">
-        <v>-82.39730265600002</v>
+        <v>-83.558910048</v>
       </c>
       <c r="Q70">
-        <v>11.00269734399998</v>
+        <v>9.841089952000004</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1768464715792642</v>
+        <v>0.1810737771140792</v>
       </c>
       <c r="T70">
-        <v>3.026477403678157</v>
+        <v>3.124105707022613</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.01208062317192158</v>
+        <v>-0.01190554167667634</v>
       </c>
       <c r="W70">
-        <v>0.2386486109439391</v>
+        <v>0.2386073267273603</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.04314508275686268</v>
+        <v>-0.04251979170241538</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7062,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2207719263472431</v>
+        <v>0.2226719263472431</v>
       </c>
       <c r="C71">
-        <v>-222.8104369185338</v>
+        <v>-231.6145686135702</v>
       </c>
       <c r="D71">
-        <v>230.2875630814663</v>
+        <v>228.3254313864299</v>
       </c>
       <c r="E71">
-        <v>-10.90199999999993</v>
+        <v>-4.059999999999945</v>
       </c>
       <c r="F71">
-        <v>472.0980000000001</v>
+        <v>478.9400000000001</v>
       </c>
       <c r="G71">
         <v>19</v>
@@ -7098,37 +7109,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M71">
-        <v>111.3207084</v>
+        <v>112.934052</v>
       </c>
       <c r="N71">
-        <v>-116.0540417333333</v>
+        <v>-117.6673853333334</v>
       </c>
       <c r="O71">
-        <v>-32.49513168533334</v>
+        <v>-32.94686789333334</v>
       </c>
       <c r="P71">
-        <v>-83.558910048</v>
+        <v>-84.72051744000001</v>
       </c>
       <c r="Q71">
-        <v>9.841089952000004</v>
+        <v>8.679482559999997</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1810737771140792</v>
+        <v>0.1855829030178818</v>
       </c>
       <c r="T71">
-        <v>3.124105707022613</v>
+        <v>3.228242563923367</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.01190554167667634</v>
+        <v>-0.01173546250986667</v>
       </c>
       <c r="W71">
-        <v>0.2386073267273603</v>
+        <v>0.2385672220598266</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.04251979170241538</v>
+        <v>-0.04191236610666671</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7144,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2226719263472431</v>
+        <v>0.2245719263472432</v>
       </c>
       <c r="C72">
-        <v>-231.6145686135702</v>
+        <v>-240.3855466737452</v>
       </c>
       <c r="D72">
-        <v>228.3254313864299</v>
+        <v>226.3964533262549</v>
       </c>
       <c r="E72">
-        <v>-4.059999999999945</v>
+        <v>2.782000000000096</v>
       </c>
       <c r="F72">
-        <v>478.9400000000001</v>
+        <v>485.7820000000001</v>
       </c>
       <c r="G72">
         <v>19</v>
@@ -7180,37 +7191,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M72">
-        <v>112.934052</v>
+        <v>114.5473956</v>
       </c>
       <c r="N72">
-        <v>-117.6673853333334</v>
+        <v>-119.2807289333334</v>
       </c>
       <c r="O72">
-        <v>-32.94686789333334</v>
+        <v>-33.39860410133335</v>
       </c>
       <c r="P72">
-        <v>-84.72051744000001</v>
+        <v>-85.88212483200002</v>
       </c>
       <c r="Q72">
-        <v>8.679482559999997</v>
+        <v>7.517875167999989</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1855829030178818</v>
+        <v>0.1904030031219467</v>
       </c>
       <c r="T72">
-        <v>3.228242563923367</v>
+        <v>3.339561273024174</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.01173546250986667</v>
+        <v>-0.01157017430550235</v>
       </c>
       <c r="W72">
-        <v>0.2385672220598266</v>
+        <v>0.2385282471012375</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.04191236610666671</v>
+        <v>-0.04132205109107989</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7226,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2245719263472431</v>
+        <v>0.2264719263472431</v>
       </c>
       <c r="C73">
-        <v>-240.3855466737451</v>
+        <v>-249.1242043421795</v>
       </c>
       <c r="D73">
-        <v>226.3964533262549</v>
+        <v>224.4997956578205</v>
       </c>
       <c r="E73">
-        <v>2.781999999999982</v>
+        <v>9.624000000000024</v>
       </c>
       <c r="F73">
-        <v>485.782</v>
+        <v>492.624</v>
       </c>
       <c r="G73">
         <v>19</v>
@@ -7262,37 +7273,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M73">
-        <v>114.5473956</v>
+        <v>116.1607392</v>
       </c>
       <c r="N73">
-        <v>-119.2807289333333</v>
+        <v>-120.8940725333333</v>
       </c>
       <c r="O73">
-        <v>-33.39860410133334</v>
+        <v>-33.85034030933334</v>
       </c>
       <c r="P73">
-        <v>-85.88212483199999</v>
+        <v>-87.043732224</v>
       </c>
       <c r="Q73">
-        <v>7.517875168000018</v>
+        <v>6.35626777600001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1904030031219467</v>
+        <v>0.1955673960905876</v>
       </c>
       <c r="T73">
-        <v>3.339561273024172</v>
+        <v>3.458831318489321</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.01157017430550236</v>
+        <v>-0.01140947744014816</v>
       </c>
       <c r="W73">
-        <v>0.2385282471012375</v>
+        <v>0.2384903547803869</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.04132205109107989</v>
+        <v>-0.04074813371481478</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7308,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2264719263472431</v>
+        <v>0.2283719263472432</v>
       </c>
       <c r="C74">
-        <v>-249.1242043421795</v>
+        <v>-257.8313471716812</v>
       </c>
       <c r="D74">
-        <v>224.4997956578205</v>
+        <v>222.6346528283188</v>
       </c>
       <c r="E74">
-        <v>9.624000000000024</v>
+        <v>16.46600000000001</v>
       </c>
       <c r="F74">
-        <v>492.624</v>
+        <v>499.466</v>
       </c>
       <c r="G74">
         <v>19</v>
@@ -7344,37 +7355,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M74">
-        <v>116.1607392</v>
+        <v>117.7740828</v>
       </c>
       <c r="N74">
-        <v>-120.8940725333333</v>
+        <v>-122.5074161333333</v>
       </c>
       <c r="O74">
-        <v>-33.85034030933334</v>
+        <v>-34.30207651733334</v>
       </c>
       <c r="P74">
-        <v>-87.043732224</v>
+        <v>-88.205339616</v>
       </c>
       <c r="Q74">
-        <v>6.35626777600001</v>
+        <v>5.194660384000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1955673960905876</v>
+        <v>0.2011143366865353</v>
       </c>
       <c r="T74">
-        <v>3.458831318489321</v>
+        <v>3.586936182137074</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.01140947744014816</v>
+        <v>-0.01125318322863928</v>
       </c>
       <c r="W74">
-        <v>0.2384903547803869</v>
+        <v>0.2384535006053132</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.04074813371481478</v>
+        <v>-0.04018994010228316</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7390,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2283719263472432</v>
+        <v>0.2302719263472431</v>
       </c>
       <c r="C75">
-        <v>-257.8313471716812</v>
+        <v>-266.5077541655214</v>
       </c>
       <c r="D75">
-        <v>222.6346528283188</v>
+        <v>220.8002458344787</v>
       </c>
       <c r="E75">
-        <v>16.46600000000001</v>
+        <v>23.30800000000005</v>
       </c>
       <c r="F75">
-        <v>499.466</v>
+        <v>506.308</v>
       </c>
       <c r="G75">
         <v>19</v>
@@ -7426,37 +7437,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M75">
-        <v>117.7740828</v>
+        <v>119.3874264</v>
       </c>
       <c r="N75">
-        <v>-122.5074161333333</v>
+        <v>-124.1207597333333</v>
       </c>
       <c r="O75">
-        <v>-34.30207651733334</v>
+        <v>-34.75381272533334</v>
       </c>
       <c r="P75">
-        <v>-88.205339616</v>
+        <v>-89.36694700800001</v>
       </c>
       <c r="Q75">
-        <v>5.194660384000002</v>
+        <v>4.033052991999995</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2011143366865353</v>
+        <v>0.2070879650206328</v>
       </c>
       <c r="T75">
-        <v>3.586936182137074</v>
+        <v>3.724895266065423</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.01125318322863928</v>
+        <v>-0.01110111318500902</v>
       </c>
       <c r="W75">
-        <v>0.2384535006053132</v>
+        <v>0.2384176424890251</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.04018994010228316</v>
+        <v>-0.0396468328036037</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7472,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2302719263472431</v>
+        <v>0.2321719263472432</v>
       </c>
       <c r="C76">
-        <v>-266.5077541655214</v>
+        <v>-275.154178862276</v>
       </c>
       <c r="D76">
-        <v>220.8002458344787</v>
+        <v>218.9958211377241</v>
       </c>
       <c r="E76">
-        <v>23.30800000000005</v>
+        <v>30.15000000000009</v>
       </c>
       <c r="F76">
-        <v>506.308</v>
+        <v>513.1500000000001</v>
       </c>
       <c r="G76">
         <v>19</v>
@@ -7508,37 +7519,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M76">
-        <v>119.3874264</v>
+        <v>121.00077</v>
       </c>
       <c r="N76">
-        <v>-124.1207597333333</v>
+        <v>-125.7341033333334</v>
       </c>
       <c r="O76">
-        <v>-34.75381272533334</v>
+        <v>-35.20554893333335</v>
       </c>
       <c r="P76">
-        <v>-89.36694700800001</v>
+        <v>-90.52855440000002</v>
       </c>
       <c r="Q76">
-        <v>4.033052991999995</v>
+        <v>2.871445599999987</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2070879650206328</v>
+        <v>0.2135394836214582</v>
       </c>
       <c r="T76">
-        <v>3.724895266065423</v>
+        <v>3.873891076708041</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.01110111318500902</v>
+        <v>-0.01095309834254223</v>
       </c>
       <c r="W76">
-        <v>0.2384176424890251</v>
+        <v>0.2383827405891715</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.0396468328036037</v>
+        <v>-0.03911820836622226</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7554,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2321719263472432</v>
+        <v>0.2340719263472431</v>
       </c>
       <c r="C77">
-        <v>-275.154178862276</v>
+        <v>-283.7713503679049</v>
       </c>
       <c r="D77">
-        <v>218.9958211377241</v>
+        <v>217.2206496320952</v>
       </c>
       <c r="E77">
-        <v>30.15000000000009</v>
+        <v>36.99200000000008</v>
       </c>
       <c r="F77">
-        <v>513.1500000000001</v>
+        <v>519.9920000000001</v>
       </c>
       <c r="G77">
         <v>19</v>
@@ -7590,37 +7601,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M77">
-        <v>121.00077</v>
+        <v>122.6141136</v>
       </c>
       <c r="N77">
-        <v>-125.7341033333334</v>
+        <v>-127.3474469333334</v>
       </c>
       <c r="O77">
-        <v>-35.20554893333335</v>
+        <v>-35.65728514133335</v>
       </c>
       <c r="P77">
-        <v>-90.52855440000002</v>
+        <v>-91.69016179200001</v>
       </c>
       <c r="Q77">
-        <v>2.871445599999987</v>
+        <v>1.709838207999994</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2135394836214582</v>
+        <v>0.2205286287723522</v>
       </c>
       <c r="T77">
-        <v>3.873891076708041</v>
+        <v>4.035303204904208</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.01095309834254223</v>
+        <v>-0.01080897862750878</v>
       </c>
       <c r="W77">
-        <v>0.2383827405891715</v>
+        <v>0.2383487571603666</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.03911820836622226</v>
+        <v>-0.03860349509824568</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7636,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2340719263472431</v>
+        <v>0.2359719263472431</v>
       </c>
       <c r="C78">
-        <v>-283.7713503679049</v>
+        <v>-292.3599743380387</v>
       </c>
       <c r="D78">
-        <v>217.2206496320952</v>
+        <v>215.4740256619614</v>
       </c>
       <c r="E78">
-        <v>36.99200000000008</v>
+        <v>43.83400000000006</v>
       </c>
       <c r="F78">
-        <v>519.9920000000001</v>
+        <v>526.8340000000001</v>
       </c>
       <c r="G78">
         <v>19</v>
@@ -7672,37 +7683,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M78">
-        <v>122.6141136</v>
+        <v>124.2274572</v>
       </c>
       <c r="N78">
-        <v>-127.3474469333334</v>
+        <v>-128.9607905333334</v>
       </c>
       <c r="O78">
-        <v>-35.65728514133335</v>
+        <v>-36.10902134933334</v>
       </c>
       <c r="P78">
-        <v>-91.69016179200001</v>
+        <v>-92.85176918400001</v>
       </c>
       <c r="Q78">
-        <v>1.709838207999994</v>
+        <v>0.5482308160000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2205286287723522</v>
+        <v>0.228125525675498</v>
       </c>
       <c r="T78">
-        <v>4.035303204904208</v>
+        <v>4.210751170334827</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.01080897862750878</v>
+        <v>-0.01066860228169698</v>
       </c>
       <c r="W78">
-        <v>0.2383487571603666</v>
+        <v>0.2383156564180242</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.03860349509824568</v>
+        <v>-0.03810215100606062</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7718,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2359719263472431</v>
+        <v>0.2378719263472431</v>
       </c>
       <c r="C79">
-        <v>-292.3599743380387</v>
+        <v>-300.9207339132529</v>
       </c>
       <c r="D79">
-        <v>215.4740256619614</v>
+        <v>213.7552660867471</v>
       </c>
       <c r="E79">
-        <v>43.83400000000006</v>
+        <v>50.67600000000004</v>
       </c>
       <c r="F79">
-        <v>526.8340000000001</v>
+        <v>533.676</v>
       </c>
       <c r="G79">
         <v>19</v>
@@ -7754,37 +7765,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M79">
-        <v>124.2274572</v>
+        <v>125.8408008</v>
       </c>
       <c r="N79">
-        <v>-128.9607905333334</v>
+        <v>-130.5741341333334</v>
       </c>
       <c r="O79">
-        <v>-36.10902134933334</v>
+        <v>-36.56075755733335</v>
       </c>
       <c r="P79">
-        <v>-92.85176918400001</v>
+        <v>-94.01337657600001</v>
       </c>
       <c r="Q79">
-        <v>0.5482308160000002</v>
+        <v>-0.6133765760000074</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.228125525675498</v>
+        <v>0.2364130495698388</v>
       </c>
       <c r="T79">
-        <v>4.210751170334827</v>
+        <v>4.402148950804591</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.01066860228169698</v>
+        <v>-0.01053182532936753</v>
       </c>
       <c r="W79">
-        <v>0.2383156564180242</v>
+        <v>0.2382834044126649</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.03810215100606062</v>
+        <v>-0.03761366189059845</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7800,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2378719263472431</v>
+        <v>0.2397719263472431</v>
       </c>
       <c r="C80">
-        <v>-300.9207339132529</v>
+        <v>-309.4542906099355</v>
       </c>
       <c r="D80">
-        <v>213.7552660867471</v>
+        <v>212.0637093900646</v>
       </c>
       <c r="E80">
-        <v>50.67600000000004</v>
+        <v>57.51800000000003</v>
       </c>
       <c r="F80">
-        <v>533.676</v>
+        <v>540.518</v>
       </c>
       <c r="G80">
         <v>19</v>
@@ -7836,37 +7847,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M80">
-        <v>125.8408008</v>
+        <v>127.4541444</v>
       </c>
       <c r="N80">
-        <v>-130.5741341333334</v>
+        <v>-132.1874777333334</v>
       </c>
       <c r="O80">
-        <v>-36.56075755733335</v>
+        <v>-37.01249376533335</v>
       </c>
       <c r="P80">
-        <v>-94.01337657600001</v>
+        <v>-95.17498396800002</v>
       </c>
       <c r="Q80">
-        <v>-0.6133765760000074</v>
+        <v>-1.774983968000015</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2364130495698388</v>
+        <v>0.2454898614541169</v>
       </c>
       <c r="T80">
-        <v>4.402148950804591</v>
+        <v>4.611775091319096</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.01053182532936753</v>
+        <v>-0.01039851108469199</v>
       </c>
       <c r="W80">
-        <v>0.2382834044126649</v>
+        <v>0.2382519689137704</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.03761366189059845</v>
+        <v>-0.03713753958818589</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7882,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2397719263472431</v>
+        <v>0.2416719263472431</v>
       </c>
       <c r="C81">
-        <v>-309.4542906099355</v>
+        <v>-317.9612851691854</v>
       </c>
       <c r="D81">
-        <v>212.0637093900646</v>
+        <v>210.3987148308146</v>
       </c>
       <c r="E81">
-        <v>57.51800000000003</v>
+        <v>64.36000000000001</v>
       </c>
       <c r="F81">
-        <v>540.518</v>
+        <v>547.36</v>
       </c>
       <c r="G81">
         <v>19</v>
@@ -7918,37 +7929,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M81">
-        <v>127.4541444</v>
+        <v>129.067488</v>
       </c>
       <c r="N81">
-        <v>-132.1874777333334</v>
+        <v>-133.8008213333333</v>
       </c>
       <c r="O81">
-        <v>-37.01249376533335</v>
+        <v>-37.46422997333333</v>
       </c>
       <c r="P81">
-        <v>-95.17498396800002</v>
+        <v>-96.33659135999999</v>
       </c>
       <c r="Q81">
-        <v>-1.774983968000015</v>
+        <v>-2.93659135999998</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2454898614541169</v>
+        <v>0.2554743545268227</v>
       </c>
       <c r="T81">
-        <v>4.611775091319096</v>
+        <v>4.842363845885051</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.01039851108469199</v>
+        <v>-0.01026852969613334</v>
       </c>
       <c r="W81">
-        <v>0.2382519689137704</v>
+        <v>0.2382213193023482</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.03713753958818589</v>
+        <v>-0.03667332034333315</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7964,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2416719263472431</v>
+        <v>0.2435719263472431</v>
       </c>
       <c r="C82">
-        <v>-317.9612851691854</v>
+        <v>-326.4423383660343</v>
       </c>
       <c r="D82">
-        <v>210.3987148308146</v>
+        <v>208.7596616339658</v>
       </c>
       <c r="E82">
-        <v>64.36000000000001</v>
+        <v>71.20200000000011</v>
       </c>
       <c r="F82">
-        <v>547.36</v>
+        <v>554.2020000000001</v>
       </c>
       <c r="G82">
         <v>19</v>
@@ -8000,37 +8011,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M82">
-        <v>129.067488</v>
+        <v>130.6808316</v>
       </c>
       <c r="N82">
-        <v>-133.8008213333333</v>
+        <v>-135.4141649333334</v>
       </c>
       <c r="O82">
-        <v>-37.46422997333333</v>
+        <v>-37.91596618133335</v>
       </c>
       <c r="P82">
-        <v>-96.33659135999999</v>
+        <v>-97.49819875200004</v>
       </c>
       <c r="Q82">
-        <v>-2.93659135999998</v>
+        <v>-4.09819875200003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2554743545268227</v>
+        <v>0.2665098468703397</v>
       </c>
       <c r="T82">
-        <v>4.842363845885051</v>
+        <v>5.097225100931633</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.01026852969613334</v>
+        <v>-0.01014175772457614</v>
       </c>
       <c r="W82">
-        <v>0.2382213193023482</v>
+        <v>0.2381914264714551</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.03667332034333315</v>
+        <v>-0.03622056330205781</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8046,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2435719263472431</v>
+        <v>0.2454719263472431</v>
       </c>
       <c r="C83">
-        <v>-326.4423383660343</v>
+        <v>-334.8980517811349</v>
       </c>
       <c r="D83">
-        <v>208.7596616339658</v>
+        <v>207.1459482188652</v>
       </c>
       <c r="E83">
-        <v>71.20200000000011</v>
+        <v>78.0440000000001</v>
       </c>
       <c r="F83">
-        <v>554.2020000000001</v>
+        <v>561.0440000000001</v>
       </c>
       <c r="G83">
         <v>19</v>
@@ -8082,37 +8093,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M83">
-        <v>130.6808316</v>
+        <v>132.2941752</v>
       </c>
       <c r="N83">
-        <v>-135.4141649333334</v>
+        <v>-137.0275085333334</v>
       </c>
       <c r="O83">
-        <v>-37.91596618133335</v>
+        <v>-38.36770238933335</v>
       </c>
       <c r="P83">
-        <v>-97.49819875200004</v>
+        <v>-98.65980614400004</v>
       </c>
       <c r="Q83">
-        <v>-4.09819875200003</v>
+        <v>-5.259806144000038</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2665098468703397</v>
+        <v>0.278771505029803</v>
       </c>
       <c r="T83">
-        <v>5.097225100931633</v>
+        <v>5.380404273205612</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.01014175772457614</v>
+        <v>-0.01001807775232521</v>
       </c>
       <c r="W83">
-        <v>0.2381914264714551</v>
+        <v>0.2381622627339983</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.03622056330205781</v>
+        <v>-0.03577884911544738</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8128,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2454719263472431</v>
+        <v>0.2473719263472431</v>
       </c>
       <c r="C84">
-        <v>-334.8980517811349</v>
+        <v>-343.3290085369343</v>
       </c>
       <c r="D84">
-        <v>207.1459482188652</v>
+        <v>205.5569914630658</v>
       </c>
       <c r="E84">
-        <v>78.0440000000001</v>
+        <v>84.88600000000008</v>
       </c>
       <c r="F84">
-        <v>561.0440000000001</v>
+        <v>567.8860000000001</v>
       </c>
       <c r="G84">
         <v>19</v>
@@ -8164,37 +8175,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M84">
-        <v>132.2941752</v>
+        <v>133.9075188</v>
       </c>
       <c r="N84">
-        <v>-137.0275085333334</v>
+        <v>-138.6408521333333</v>
       </c>
       <c r="O84">
-        <v>-38.36770238933335</v>
+        <v>-38.81943859733334</v>
       </c>
       <c r="P84">
-        <v>-98.65980614400004</v>
+        <v>-99.82141353599999</v>
       </c>
       <c r="Q84">
-        <v>-5.259806144000038</v>
+        <v>-6.421413535999989</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.278771505029803</v>
+        <v>0.2924757112080267</v>
       </c>
       <c r="T84">
-        <v>5.380404273205612</v>
+        <v>5.696898642217707</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.01001807775232521</v>
+        <v>-0.009897378020369486</v>
       </c>
       <c r="W84">
-        <v>0.2381622627339983</v>
+        <v>0.2381338017372031</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.03577884911544738</v>
+        <v>-0.03534777864417671</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8210,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2473719263472431</v>
+        <v>0.2492719263472432</v>
       </c>
       <c r="C85">
-        <v>-343.3290085369343</v>
+        <v>-351.7357740002222</v>
       </c>
       <c r="D85">
-        <v>205.5569914630658</v>
+        <v>203.9922259997779</v>
       </c>
       <c r="E85">
-        <v>84.88600000000008</v>
+        <v>91.72800000000007</v>
       </c>
       <c r="F85">
-        <v>567.8860000000001</v>
+        <v>574.7280000000001</v>
       </c>
       <c r="G85">
         <v>19</v>
@@ -8246,37 +8257,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M85">
-        <v>133.9075188</v>
+        <v>135.5208624</v>
       </c>
       <c r="N85">
-        <v>-138.6408521333333</v>
+        <v>-140.2541957333333</v>
       </c>
       <c r="O85">
-        <v>-38.81943859733334</v>
+        <v>-39.27117480533334</v>
       </c>
       <c r="P85">
-        <v>-99.82141353599999</v>
+        <v>-100.983020928</v>
       </c>
       <c r="Q85">
-        <v>-6.421413535999989</v>
+        <v>-7.583020927999996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2924757112080267</v>
+        <v>0.3078929431585284</v>
       </c>
       <c r="T85">
-        <v>5.696898642217707</v>
+        <v>6.052954807356316</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.009897378020369486</v>
+        <v>-0.00977955209155556</v>
       </c>
       <c r="W85">
-        <v>0.2381338017372031</v>
+        <v>0.2381060183831888</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.03534777864417671</v>
+        <v>-0.03492697175555537</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8292,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2492719263472432</v>
+        <v>0.2511719263472432</v>
       </c>
       <c r="C86">
-        <v>-351.7357740002222</v>
+        <v>-360.1188964528342</v>
       </c>
       <c r="D86">
-        <v>203.9922259997779</v>
+        <v>202.4511035471658</v>
       </c>
       <c r="E86">
-        <v>91.72800000000007</v>
+        <v>98.57000000000005</v>
       </c>
       <c r="F86">
-        <v>574.7280000000001</v>
+        <v>581.5700000000001</v>
       </c>
       <c r="G86">
         <v>19</v>
@@ -8328,37 +8339,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M86">
-        <v>135.5208624</v>
+        <v>137.134206</v>
       </c>
       <c r="N86">
-        <v>-140.2541957333333</v>
+        <v>-141.8675393333334</v>
       </c>
       <c r="O86">
-        <v>-39.27117480533334</v>
+        <v>-39.72291101333334</v>
       </c>
       <c r="P86">
-        <v>-100.983020928</v>
+        <v>-102.14462832</v>
       </c>
       <c r="Q86">
-        <v>-7.583020927999996</v>
+        <v>-8.744628320000004</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3078929431585283</v>
+        <v>0.3253658060357636</v>
       </c>
       <c r="T86">
-        <v>6.052954807356311</v>
+        <v>6.456485127846734</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.00977955209155556</v>
+        <v>-0.009664498537537262</v>
       </c>
       <c r="W86">
-        <v>0.2381060183831888</v>
+        <v>0.2380788887551513</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.03492697175555537</v>
+        <v>-0.03451606620549041</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8374,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2511719263472432</v>
+        <v>0.2530719263472431</v>
       </c>
       <c r="C87">
-        <v>-360.1188964528342</v>
+        <v>-368.4789077321809</v>
       </c>
       <c r="D87">
-        <v>202.4511035471658</v>
+        <v>200.9330922678191</v>
       </c>
       <c r="E87">
-        <v>98.57000000000005</v>
+        <v>105.412</v>
       </c>
       <c r="F87">
-        <v>581.5700000000001</v>
+        <v>588.412</v>
       </c>
       <c r="G87">
         <v>19</v>
@@ -8410,37 +8421,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M87">
-        <v>137.134206</v>
+        <v>138.7475496</v>
       </c>
       <c r="N87">
-        <v>-141.8675393333334</v>
+        <v>-143.4808829333334</v>
       </c>
       <c r="O87">
-        <v>-39.72291101333334</v>
+        <v>-40.17464722133334</v>
       </c>
       <c r="P87">
-        <v>-102.14462832</v>
+        <v>-103.306235712</v>
       </c>
       <c r="Q87">
-        <v>-8.744628320000004</v>
+        <v>-9.906235712000012</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3253658060357636</v>
+        <v>0.3453347921811752</v>
       </c>
       <c r="T87">
-        <v>6.456485127846734</v>
+        <v>6.917662636978642</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.009664498537537262</v>
+        <v>-0.009552120647565897</v>
       </c>
       <c r="W87">
-        <v>0.2380788887551513</v>
+        <v>0.238052390048696</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.03451606620549041</v>
+        <v>-0.03411471659844967</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8456,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2530719263472431</v>
+        <v>0.2549719263472431</v>
       </c>
       <c r="C88">
-        <v>-368.4789077321809</v>
+        <v>-376.816323843174</v>
       </c>
       <c r="D88">
-        <v>200.9330922678191</v>
+        <v>199.437676156826</v>
       </c>
       <c r="E88">
-        <v>105.412</v>
+        <v>112.254</v>
       </c>
       <c r="F88">
-        <v>588.412</v>
+        <v>595.254</v>
       </c>
       <c r="G88">
         <v>19</v>
@@ -8492,37 +8503,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M88">
-        <v>138.7475496</v>
+        <v>140.3608932</v>
       </c>
       <c r="N88">
-        <v>-143.4808829333334</v>
+        <v>-145.0942265333334</v>
       </c>
       <c r="O88">
-        <v>-40.17464722133334</v>
+        <v>-40.62638342933334</v>
       </c>
       <c r="P88">
-        <v>-103.306235712</v>
+        <v>-104.467843104</v>
       </c>
       <c r="Q88">
-        <v>-9.906235712000012</v>
+        <v>-11.06784310400002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3453347921811752</v>
+        <v>0.3683759300412656</v>
       </c>
       <c r="T88">
-        <v>6.917662636978642</v>
+        <v>7.449790532130845</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.009552120647565897</v>
+        <v>-0.009442326157363991</v>
       </c>
       <c r="W88">
-        <v>0.238052390048696</v>
+        <v>0.2380265005079064</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.03411471659844967</v>
+        <v>-0.03372259341915718</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8538,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2549719263472431</v>
+        <v>0.2568719263472432</v>
       </c>
       <c r="C89">
-        <v>-376.816323843174</v>
+        <v>-385.1316455430298</v>
       </c>
       <c r="D89">
-        <v>199.437676156826</v>
+        <v>197.9643544569703</v>
       </c>
       <c r="E89">
-        <v>112.254</v>
+        <v>119.096</v>
       </c>
       <c r="F89">
-        <v>595.254</v>
+        <v>602.096</v>
       </c>
       <c r="G89">
         <v>19</v>
@@ -8574,37 +8585,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M89">
-        <v>140.3608932</v>
+        <v>141.9742368</v>
       </c>
       <c r="N89">
-        <v>-145.0942265333334</v>
+        <v>-146.7075701333333</v>
       </c>
       <c r="O89">
-        <v>-40.62638342933334</v>
+        <v>-41.07811963733333</v>
       </c>
       <c r="P89">
-        <v>-104.467843104</v>
+        <v>-105.629450496</v>
       </c>
       <c r="Q89">
-        <v>-11.06784310400002</v>
+        <v>-12.22945049599998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3683759300412656</v>
+        <v>0.3952572575447045</v>
       </c>
       <c r="T89">
-        <v>7.449790532130845</v>
+        <v>8.070606409808418</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.009442326157363991</v>
+        <v>-0.009335026996484856</v>
       </c>
       <c r="W89">
-        <v>0.2380265005079064</v>
+        <v>0.2380011993657712</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.03372259341915718</v>
+        <v>-0.03333938213030296</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8620,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2568719263472432</v>
+        <v>0.2587719263472431</v>
       </c>
       <c r="C90">
-        <v>-385.1316455430298</v>
+        <v>-393.4253589003416</v>
       </c>
       <c r="D90">
-        <v>197.9643544569703</v>
+        <v>196.5126410996585</v>
       </c>
       <c r="E90">
-        <v>119.096</v>
+        <v>125.9380000000001</v>
       </c>
       <c r="F90">
-        <v>602.096</v>
+        <v>608.9380000000001</v>
       </c>
       <c r="G90">
         <v>19</v>
@@ -8656,37 +8667,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M90">
-        <v>141.9742368</v>
+        <v>143.5875804</v>
       </c>
       <c r="N90">
-        <v>-146.7075701333333</v>
+        <v>-148.3209137333334</v>
       </c>
       <c r="O90">
-        <v>-41.07811963733333</v>
+        <v>-41.52985584533335</v>
       </c>
       <c r="P90">
-        <v>-105.629450496</v>
+        <v>-106.791057888</v>
       </c>
       <c r="Q90">
-        <v>-12.22945049599998</v>
+        <v>-13.39105788800003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3952572575447045</v>
+        <v>0.4270260991396776</v>
       </c>
       <c r="T90">
-        <v>8.070606409808418</v>
+        <v>8.804297901609182</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.009335026996484856</v>
+        <v>-0.009230139052704124</v>
       </c>
       <c r="W90">
-        <v>0.2380011993657712</v>
+        <v>0.2379764667886276</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.03333938213030296</v>
+        <v>-0.03296478233108635</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8702,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2587719263472431</v>
+        <v>0.2606719263472432</v>
       </c>
       <c r="C91">
-        <v>-393.4253589003416</v>
+        <v>-401.6979358297328</v>
       </c>
       <c r="D91">
-        <v>196.5126410996585</v>
+        <v>195.0820641702673</v>
       </c>
       <c r="E91">
-        <v>125.9380000000001</v>
+        <v>132.7800000000001</v>
       </c>
       <c r="F91">
-        <v>608.9380000000001</v>
+        <v>615.7800000000001</v>
       </c>
       <c r="G91">
         <v>19</v>
@@ -8738,37 +8749,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M91">
-        <v>143.5875804</v>
+        <v>145.200924</v>
       </c>
       <c r="N91">
-        <v>-148.3209137333334</v>
+        <v>-149.9342573333333</v>
       </c>
       <c r="O91">
-        <v>-41.52985584533335</v>
+        <v>-41.98159205333334</v>
       </c>
       <c r="P91">
-        <v>-106.791057888</v>
+        <v>-107.95266528</v>
       </c>
       <c r="Q91">
-        <v>-13.39105788800003</v>
+        <v>-14.55266527999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4270260991396776</v>
+        <v>0.4651487090536454</v>
       </c>
       <c r="T91">
-        <v>8.804297901609182</v>
+        <v>9.684727691770101</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.009230139052704124</v>
+        <v>-0.009127581952118524</v>
       </c>
       <c r="W91">
-        <v>0.2379764667886276</v>
+        <v>0.2379522838243096</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.03296478233108635</v>
+        <v>-0.03259850697185174</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8784,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2606719263472432</v>
+        <v>0.2625719263472431</v>
       </c>
       <c r="C92">
-        <v>-401.6979358297328</v>
+        <v>-409.9498346033246</v>
       </c>
       <c r="D92">
-        <v>195.0820641702673</v>
+        <v>193.6721653966755</v>
       </c>
       <c r="E92">
-        <v>132.7800000000001</v>
+        <v>139.6220000000001</v>
       </c>
       <c r="F92">
-        <v>615.7800000000001</v>
+        <v>622.6220000000001</v>
       </c>
       <c r="G92">
         <v>19</v>
@@ -8820,37 +8831,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M92">
-        <v>145.200924</v>
+        <v>146.8142676</v>
       </c>
       <c r="N92">
-        <v>-149.9342573333333</v>
+        <v>-151.5476009333333</v>
       </c>
       <c r="O92">
-        <v>-41.98159205333334</v>
+        <v>-42.43332826133334</v>
       </c>
       <c r="P92">
-        <v>-107.95266528</v>
+        <v>-109.114272672</v>
       </c>
       <c r="Q92">
-        <v>-14.55266527999999</v>
+        <v>-15.71427267199999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4651487090536454</v>
+        <v>0.511743010059606</v>
       </c>
       <c r="T92">
-        <v>9.684727691770101</v>
+        <v>10.76080854641122</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.009127581952118524</v>
+        <v>-0.009027278853743596</v>
       </c>
       <c r="W92">
-        <v>0.2379522838243096</v>
+        <v>0.2379286323537127</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.03259850697185174</v>
+        <v>-0.03224028162051273</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8866,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2625719263472431</v>
+        <v>0.2644719263472431</v>
       </c>
       <c r="C93">
-        <v>-409.9498346033246</v>
+        <v>-418.1815003401856</v>
       </c>
       <c r="D93">
-        <v>193.6721653966755</v>
+        <v>192.2824996598145</v>
       </c>
       <c r="E93">
-        <v>139.6220000000001</v>
+        <v>146.4640000000001</v>
       </c>
       <c r="F93">
-        <v>622.6220000000001</v>
+        <v>629.4640000000001</v>
       </c>
       <c r="G93">
         <v>19</v>
@@ -8902,37 +8913,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M93">
-        <v>146.8142676</v>
+        <v>148.4276112</v>
       </c>
       <c r="N93">
-        <v>-151.5476009333333</v>
+        <v>-153.1609445333333</v>
       </c>
       <c r="O93">
-        <v>-42.43332826133334</v>
+        <v>-42.88506446933334</v>
       </c>
       <c r="P93">
-        <v>-109.114272672</v>
+        <v>-110.275880064</v>
       </c>
       <c r="Q93">
-        <v>-15.71427267199999</v>
+        <v>-16.875880064</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.511743010059606</v>
+        <v>0.5699858863170569</v>
       </c>
       <c r="T93">
-        <v>10.76080854641122</v>
+        <v>12.10590961471263</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.009027278853743596</v>
+        <v>-0.008929156257507252</v>
       </c>
       <c r="W93">
-        <v>0.2379286323537127</v>
+        <v>0.2379054950455202</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.03224028162051273</v>
+        <v>-0.03188984377681159</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8948,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2644719263472431</v>
+        <v>0.2663719263472431</v>
       </c>
       <c r="C94">
-        <v>-418.1815003401856</v>
+        <v>-426.3933654748581</v>
       </c>
       <c r="D94">
-        <v>192.2824996598145</v>
+        <v>190.9126345251419</v>
       </c>
       <c r="E94">
-        <v>146.4640000000001</v>
+        <v>153.306</v>
       </c>
       <c r="F94">
-        <v>629.4640000000001</v>
+        <v>636.306</v>
       </c>
       <c r="G94">
         <v>19</v>
@@ -8984,37 +8995,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M94">
-        <v>148.4276112</v>
+        <v>150.0409548</v>
       </c>
       <c r="N94">
-        <v>-153.1609445333333</v>
+        <v>-154.7742881333334</v>
       </c>
       <c r="O94">
-        <v>-42.88506446933334</v>
+        <v>-43.33680067733334</v>
       </c>
       <c r="P94">
-        <v>-110.275880064</v>
+        <v>-111.437487456</v>
       </c>
       <c r="Q94">
-        <v>-16.875880064</v>
+        <v>-18.03748745600001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5699858863170569</v>
+        <v>0.6448695843623508</v>
       </c>
       <c r="T94">
-        <v>12.10590961471263</v>
+        <v>13.83532527395729</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.008929156257507252</v>
+        <v>-0.008833143824630832</v>
       </c>
       <c r="W94">
-        <v>0.2379054950455202</v>
+        <v>0.237882855313848</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.03188984377681159</v>
+        <v>-0.03154694223082455</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9030,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2663719263472431</v>
+        <v>0.2682719263472431</v>
       </c>
       <c r="C95">
-        <v>-426.3933654748581</v>
+        <v>-434.5858502060003</v>
       </c>
       <c r="D95">
-        <v>190.9126345251419</v>
+        <v>189.5621497939999</v>
       </c>
       <c r="E95">
-        <v>153.306</v>
+        <v>160.1480000000001</v>
       </c>
       <c r="F95">
-        <v>636.306</v>
+        <v>643.1480000000001</v>
       </c>
       <c r="G95">
         <v>19</v>
@@ -9066,37 +9077,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M95">
-        <v>150.0409548</v>
+        <v>151.6542984</v>
       </c>
       <c r="N95">
-        <v>-154.7742881333334</v>
+        <v>-156.3876317333334</v>
       </c>
       <c r="O95">
-        <v>-43.33680067733334</v>
+        <v>-43.78853688533334</v>
       </c>
       <c r="P95">
-        <v>-111.437487456</v>
+        <v>-112.599094848</v>
       </c>
       <c r="Q95">
-        <v>-18.03748745600001</v>
+        <v>-19.19909484800002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6448695843623508</v>
+        <v>0.7447145150894093</v>
       </c>
       <c r="T95">
-        <v>13.83532527395729</v>
+        <v>16.14121281961685</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.008833143824630832</v>
+        <v>-0.008739174209475183</v>
       </c>
       <c r="W95">
-        <v>0.237882855313848</v>
+        <v>0.2378606972785942</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.03154694223082455</v>
+        <v>-0.03121133646241137</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9112,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2682719263472431</v>
+        <v>0.2701719263472431</v>
       </c>
       <c r="C96">
-        <v>-434.5858502060003</v>
+        <v>-442.7593629261179</v>
       </c>
       <c r="D96">
-        <v>189.5621497939999</v>
+        <v>188.2306370738822</v>
       </c>
       <c r="E96">
-        <v>160.1480000000001</v>
+        <v>166.9900000000001</v>
       </c>
       <c r="F96">
-        <v>643.1480000000001</v>
+        <v>649.9900000000001</v>
       </c>
       <c r="G96">
         <v>19</v>
@@ -9148,37 +9159,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M96">
-        <v>151.6542984</v>
+        <v>153.267642</v>
       </c>
       <c r="N96">
-        <v>-156.3876317333334</v>
+        <v>-158.0009753333334</v>
       </c>
       <c r="O96">
-        <v>-43.78853688533334</v>
+        <v>-44.24027309333335</v>
       </c>
       <c r="P96">
-        <v>-112.599094848</v>
+        <v>-113.76070224</v>
       </c>
       <c r="Q96">
-        <v>-19.19909484800002</v>
+        <v>-20.36070224000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7447145150894093</v>
+        <v>0.8844974181072918</v>
       </c>
       <c r="T96">
-        <v>16.14121281961685</v>
+        <v>19.36945538354023</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.008739174209475183</v>
+        <v>-0.008647182902007023</v>
       </c>
       <c r="W96">
-        <v>0.2378606972785942</v>
+        <v>0.2378390057282933</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.03121133646241137</v>
+        <v>-0.03088279607859667</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9194,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2701719263472431</v>
+        <v>0.2720719263472431</v>
       </c>
       <c r="C97">
-        <v>-442.7593629261179</v>
+        <v>-450.914300633315</v>
       </c>
       <c r="D97">
-        <v>188.2306370738822</v>
+        <v>186.9176993666851</v>
       </c>
       <c r="E97">
-        <v>166.9900000000001</v>
+        <v>173.8320000000001</v>
       </c>
       <c r="F97">
-        <v>649.9900000000001</v>
+        <v>656.8320000000001</v>
       </c>
       <c r="G97">
         <v>19</v>
@@ -9230,37 +9241,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M97">
-        <v>153.267642</v>
+        <v>154.8809856</v>
       </c>
       <c r="N97">
-        <v>-158.0009753333334</v>
+        <v>-159.6143189333334</v>
       </c>
       <c r="O97">
-        <v>-44.24027309333335</v>
+        <v>-44.69200930133335</v>
       </c>
       <c r="P97">
-        <v>-113.76070224</v>
+        <v>-114.922309632</v>
       </c>
       <c r="Q97">
-        <v>-20.36070224000002</v>
+        <v>-21.52230963200003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8844974181072918</v>
+        <v>1.094171772634115</v>
       </c>
       <c r="T97">
-        <v>19.36945538354023</v>
+        <v>24.21181922942529</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.008647182902007023</v>
+        <v>-0.008557108080111116</v>
       </c>
       <c r="W97">
-        <v>0.2378390057282933</v>
+        <v>0.2378177660852902</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.03088279607859667</v>
+        <v>-0.03056110028611125</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9276,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2720719263472431</v>
+        <v>0.2739719263472431</v>
       </c>
       <c r="C98">
-        <v>-450.9143006333148</v>
+        <v>-459.0510493259281</v>
       </c>
       <c r="D98">
-        <v>186.9176993666852</v>
+        <v>185.6229506740719</v>
       </c>
       <c r="E98">
-        <v>173.832</v>
+        <v>180.674</v>
       </c>
       <c r="F98">
-        <v>656.832</v>
+        <v>663.674</v>
       </c>
       <c r="G98">
         <v>19</v>
@@ -9312,37 +9323,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M98">
-        <v>154.8809856</v>
+        <v>156.4943292</v>
       </c>
       <c r="N98">
-        <v>-159.6143189333333</v>
+        <v>-161.2276625333333</v>
       </c>
       <c r="O98">
-        <v>-44.69200930133334</v>
+        <v>-45.14374550933334</v>
       </c>
       <c r="P98">
-        <v>-114.922309632</v>
+        <v>-116.083917024</v>
       </c>
       <c r="Q98">
-        <v>-21.52230963199997</v>
+        <v>-22.68391702399998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.094171772634112</v>
+        <v>1.443629030178816</v>
       </c>
       <c r="T98">
-        <v>24.21181922942522</v>
+        <v>32.28242563923364</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.008557108080111118</v>
+        <v>-0.008468890471037807</v>
       </c>
       <c r="W98">
-        <v>0.2378177660852902</v>
+        <v>0.2377969643730707</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.03056110028611103</v>
+        <v>-0.0302460373965634</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9358,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2739719263472431</v>
+        <v>0.2758719263472431</v>
       </c>
       <c r="C99">
-        <v>-459.0510493259281</v>
+        <v>-467.1699843808749</v>
       </c>
       <c r="D99">
-        <v>185.6229506740719</v>
+        <v>184.3460156191252</v>
       </c>
       <c r="E99">
-        <v>180.674</v>
+        <v>187.5160000000001</v>
       </c>
       <c r="F99">
-        <v>663.674</v>
+        <v>670.5160000000001</v>
       </c>
       <c r="G99">
         <v>19</v>
@@ -9394,37 +9405,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M99">
-        <v>156.4943292</v>
+        <v>158.1076728</v>
       </c>
       <c r="N99">
-        <v>-161.2276625333333</v>
+        <v>-162.8410061333333</v>
       </c>
       <c r="O99">
-        <v>-45.14374550933334</v>
+        <v>-45.59548171733334</v>
       </c>
       <c r="P99">
-        <v>-116.083917024</v>
+        <v>-117.245524416</v>
       </c>
       <c r="Q99">
-        <v>-22.68391702399998</v>
+        <v>-23.84552441599999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.443629030178816</v>
+        <v>2.142543545268225</v>
       </c>
       <c r="T99">
-        <v>32.28242563923364</v>
+        <v>48.42363845885045</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.008468890471037807</v>
+        <v>-0.00838247322133334</v>
       </c>
       <c r="W99">
-        <v>0.2377969643730707</v>
+        <v>0.2377765871855904</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.0302460373965634</v>
+        <v>-0.02993740436190473</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9440,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2758719263472431</v>
+        <v>0.2777719263472431</v>
       </c>
       <c r="C100">
-        <v>-467.1699843808749</v>
+        <v>-475.2714709164907</v>
       </c>
       <c r="D100">
-        <v>184.3460156191252</v>
+        <v>183.0865290835094</v>
       </c>
       <c r="E100">
-        <v>187.5160000000001</v>
+        <v>194.3580000000001</v>
       </c>
       <c r="F100">
-        <v>670.5160000000001</v>
+        <v>677.3580000000001</v>
       </c>
       <c r="G100">
         <v>19</v>
@@ -9476,37 +9487,37 @@
         <v>-4.733333333333334</v>
       </c>
       <c r="M100">
-        <v>158.1076728</v>
+        <v>159.7210164</v>
       </c>
       <c r="N100">
-        <v>-162.8410061333333</v>
+        <v>-164.4543497333333</v>
       </c>
       <c r="O100">
-        <v>-45.59548171733334</v>
+        <v>-46.04721792533334</v>
       </c>
       <c r="P100">
-        <v>-117.245524416</v>
+        <v>-118.407131808</v>
       </c>
       <c r="Q100">
-        <v>-23.84552441599999</v>
+        <v>-25.007131808</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.142543545268225</v>
+        <v>4.239287090536449</v>
       </c>
       <c r="T100">
-        <v>48.42363845885045</v>
+        <v>96.84727691770091</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.00838247322133334</v>
+        <v>-0.008297801774653205</v>
       </c>
       <c r="W100">
-        <v>0.2377765871855904</v>
+        <v>0.2377566216584632</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.02993740436190473</v>
+        <v>-0.02963500633804705</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2777719263472431</v>
-      </c>
-      <c r="C101">
-        <v>-475.2714709164907</v>
-      </c>
-      <c r="D101">
-        <v>183.0865290835094</v>
-      </c>
-      <c r="E101">
-        <v>194.3580000000001</v>
-      </c>
-      <c r="F101">
-        <v>677.3580000000001</v>
-      </c>
-      <c r="G101">
-        <v>19</v>
-      </c>
-      <c r="H101">
-        <v>201.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>88.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="L101">
-        <v>-4.733333333333334</v>
-      </c>
-      <c r="M101">
-        <v>159.7210164</v>
-      </c>
-      <c r="N101">
-        <v>-164.4543497333333</v>
-      </c>
-      <c r="O101">
-        <v>-46.04721792533334</v>
-      </c>
-      <c r="P101">
-        <v>-118.407131808</v>
-      </c>
-      <c r="Q101">
-        <v>-25.007131808</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.239287090536449</v>
-      </c>
-      <c r="T101">
-        <v>96.84727691770091</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.008297801774653205</v>
-      </c>
-      <c r="W101">
-        <v>0.2377566216584632</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.02963500633804705</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
